--- a/data/excel/emae.xlsx
+++ b/data/excel/emae.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G272"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -483,11 +483,11 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>98.53181187213291</v>
+        <v>98.52915340919432</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>96.04912334076504</v>
+        <v>96.0498909638345</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
@@ -500,16 +500,16 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>98.02704245284784</v>
+        <v>98.02568657211117</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5122908121694962</v>
+        <v>-0.5109826073428678</v>
       </c>
       <c r="F3" t="n">
-        <v>96.66457940106535</v>
+        <v>96.66619692516286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6407721787494012</v>
+        <v>0.641651911463839</v>
       </c>
     </row>
     <row r="4">
@@ -521,16 +521,16 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>97.51832921205927</v>
+        <v>97.5223435557331</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5189519423002764</v>
+        <v>-0.513480735488443</v>
       </c>
       <c r="F4" t="n">
-        <v>97.32950538543467</v>
+        <v>97.33080895029403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6878693193403507</v>
+        <v>0.687533022164601</v>
       </c>
     </row>
     <row r="5">
@@ -542,16 +542,16 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>95.45367398805416</v>
+        <v>95.44877460421664</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.117197085601617</v>
+        <v>-2.126250124753653</v>
       </c>
       <c r="F5" t="n">
-        <v>98.02702949440008</v>
+        <v>98.02825018808032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7166625435967688</v>
+        <v>0.7165678014065264</v>
       </c>
     </row>
     <row r="6">
@@ -563,16 +563,16 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>96.92320511742082</v>
+        <v>96.92701669087563</v>
       </c>
       <c r="E6" t="n">
-        <v>1.539522857496905</v>
+        <v>1.548728197704577</v>
       </c>
       <c r="F6" t="n">
-        <v>98.75246294137705</v>
+        <v>98.75360630610982</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7400341015315632</v>
+        <v>0.7399460019308748</v>
       </c>
     </row>
     <row r="7">
@@ -584,16 +584,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>98.51378468037177</v>
+        <v>98.51487249075271</v>
       </c>
       <c r="E7" t="n">
-        <v>1.641071981703448</v>
+        <v>1.638197330411131</v>
       </c>
       <c r="F7" t="n">
-        <v>99.50030162249365</v>
+        <v>99.50129157918963</v>
       </c>
       <c r="G7" t="n">
-        <v>0.757286105927875</v>
+        <v>0.75712199386642</v>
       </c>
     </row>
     <row r="8">
@@ -605,16 +605,16 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>100.9268169961489</v>
+        <v>100.92733734624</v>
       </c>
       <c r="E8" t="n">
-        <v>2.449436212004414</v>
+        <v>2.4488331502573</v>
       </c>
       <c r="F8" t="n">
-        <v>100.2705114973276</v>
+        <v>100.2711728600933</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7740779296892271</v>
+        <v>0.7737399873758477</v>
       </c>
     </row>
     <row r="9">
@@ -626,16 +626,16 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>102.1001840550244</v>
+        <v>102.0992616267447</v>
       </c>
       <c r="E9" t="n">
-        <v>1.162591959003663</v>
+        <v>1.161156443159015</v>
       </c>
       <c r="F9" t="n">
-        <v>101.0610088461495</v>
+        <v>101.0610987742827</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7883647315821491</v>
+        <v>0.7877896424843982</v>
       </c>
     </row>
     <row r="10">
@@ -647,16 +647,16 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>102.3154156470083</v>
+        <v>102.3158177251978</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2108043134063848</v>
+        <v>0.2121034912523072</v>
       </c>
       <c r="F10" t="n">
-        <v>101.8677654171479</v>
+        <v>101.8670748014109</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7982866787195064</v>
+        <v>0.7975136198828352</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>103.237893609225</v>
+        <v>103.236940639844</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9016021255284556</v>
+        <v>0.9002742050306267</v>
       </c>
       <c r="F11" t="n">
-        <v>102.6854203615272</v>
+        <v>102.6838414608525</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8026630809373785</v>
+        <v>0.801796518682778</v>
       </c>
     </row>
     <row r="12">
@@ -689,16 +689,16 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>103.4296276369313</v>
+        <v>103.430061093373</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1857205925103926</v>
+        <v>0.1870652620390416</v>
       </c>
       <c r="F12" t="n">
-        <v>103.4983704240112</v>
+        <v>103.4959412333585</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7916898617367281</v>
+        <v>0.7908739690222433</v>
       </c>
     </row>
     <row r="13">
@@ -710,16 +710,16 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>103.0222147327755</v>
+        <v>103.0227342457169</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3939034814917193</v>
+        <v>-0.3938186281146159</v>
       </c>
       <c r="F13" t="n">
-        <v>104.2939212683006</v>
+        <v>104.2908259573307</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7686602610554587</v>
+        <v>0.7680346828093718</v>
       </c>
     </row>
     <row r="14">
@@ -733,16 +733,16 @@
         <v>6.311142071092917</v>
       </c>
       <c r="D14" t="n">
-        <v>105.8527112468244</v>
+        <v>105.8578491181189</v>
       </c>
       <c r="E14" t="n">
-        <v>2.747462303534036</v>
+        <v>2.751931302502641</v>
       </c>
       <c r="F14" t="n">
-        <v>105.0595141929546</v>
+        <v>105.0560364990156</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7340724323563705</v>
+        <v>0.7337275687105915</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         <v>6.578266051220922</v>
       </c>
       <c r="D15" t="n">
-        <v>105.9735797963941</v>
+        <v>105.9726873716051</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1141855963310263</v>
+        <v>0.108483456298103</v>
       </c>
       <c r="F15" t="n">
-        <v>105.7865158990053</v>
+        <v>105.7829833365863</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6919903557858191</v>
+        <v>0.6919610350782079</v>
       </c>
     </row>
     <row r="16">
@@ -779,16 +779,16 @@
         <v>8.610957824672226</v>
       </c>
       <c r="D16" t="n">
-        <v>106.8236802561826</v>
+        <v>106.8194348096801</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8021815073358169</v>
+        <v>0.7990242194253057</v>
       </c>
       <c r="F16" t="n">
-        <v>106.4711745834651</v>
+        <v>106.4679022538531</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6472078966221773</v>
+        <v>0.6474755160642758</v>
       </c>
     </row>
     <row r="17">
@@ -802,16 +802,16 @@
         <v>13.62787406951273</v>
       </c>
       <c r="D17" t="n">
-        <v>108.0966060252392</v>
+        <v>108.0993878125847</v>
       </c>
       <c r="E17" t="n">
-        <v>1.191613850041449</v>
+        <v>1.198239819547013</v>
       </c>
       <c r="F17" t="n">
-        <v>107.1158103083776</v>
+        <v>107.1130633602978</v>
       </c>
       <c r="G17" t="n">
-        <v>0.605455633822416</v>
+        <v>0.6059677074377277</v>
       </c>
     </row>
     <row r="18">
@@ -825,16 +825,16 @@
         <v>15.27559219364601</v>
       </c>
       <c r="D18" t="n">
-        <v>108.9827031781444</v>
+        <v>108.9779604713723</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8197270806988399</v>
+        <v>0.8127452676335309</v>
       </c>
       <c r="F18" t="n">
-        <v>107.7254243077093</v>
+        <v>107.7233692616783</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5691167322327431</v>
+        <v>0.569777282279361</v>
       </c>
     </row>
     <row r="19">
@@ -848,16 +848,16 @@
         <v>10.25891554286311</v>
       </c>
       <c r="D19" t="n">
-        <v>108.5960599379108</v>
+        <v>108.5980208573416</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3547748669819981</v>
+        <v>-0.3486389471663642</v>
       </c>
       <c r="F19" t="n">
-        <v>108.3109687375755</v>
+        <v>108.3096556791366</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5435526790720075</v>
+        <v>0.5442518382749313</v>
       </c>
     </row>
     <row r="20">
@@ -871,16 +871,16 @@
         <v>6.403258079030437</v>
       </c>
       <c r="D20" t="n">
-        <v>109.1633885176078</v>
+        <v>109.1653616788361</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5224209607801669</v>
+        <v>0.5224228001722082</v>
       </c>
       <c r="F20" t="n">
-        <v>108.8867006638653</v>
+        <v>108.88606394531</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5315545904539931</v>
+        <v>0.5321854848112366</v>
       </c>
     </row>
     <row r="21">
@@ -894,16 +894,16 @@
         <v>7.589954671411277</v>
       </c>
       <c r="D21" t="n">
-        <v>109.3096096061555</v>
+        <v>109.3119527891954</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1339470041497748</v>
+        <v>0.1342835383906902</v>
       </c>
       <c r="F21" t="n">
-        <v>109.4668963591994</v>
+        <v>109.4667407940441</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5328434894222625</v>
+        <v>0.5332884922956538</v>
       </c>
     </row>
     <row r="22">
@@ -917,16 +917,16 @@
         <v>6.938537818644079</v>
       </c>
       <c r="D22" t="n">
-        <v>109.2726022021911</v>
+        <v>109.2682858579276</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.03385558149716417</v>
+        <v>-0.03994707820473309</v>
       </c>
       <c r="F22" t="n">
-        <v>110.0654865025885</v>
+        <v>110.065560142821</v>
       </c>
       <c r="G22" t="n">
-        <v>0.546822978724947</v>
+        <v>0.5470331394113543</v>
       </c>
     </row>
     <row r="23">
@@ -940,16 +940,16 @@
         <v>6.771558549304984</v>
       </c>
       <c r="D23" t="n">
-        <v>109.9934354975062</v>
+        <v>109.9963439901644</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6596651683844215</v>
+        <v>0.6663032429953688</v>
       </c>
       <c r="F23" t="n">
-        <v>110.6935236147824</v>
+        <v>110.6935985217537</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5706031310543267</v>
+        <v>0.5706039001825047</v>
       </c>
     </row>
     <row r="24">
@@ -963,16 +963,16 @@
         <v>7.861434801010631</v>
       </c>
       <c r="D24" t="n">
-        <v>111.1467861309117</v>
+        <v>111.1448617340428</v>
       </c>
       <c r="E24" t="n">
-        <v>1.048563151236095</v>
+        <v>1.044141743457502</v>
       </c>
       <c r="F24" t="n">
-        <v>111.3615710897269</v>
+        <v>111.3614976042304</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6035108948823762</v>
+        <v>0.6033764295280974</v>
       </c>
     </row>
     <row r="25">
@@ -986,16 +986,16 @@
         <v>8.678658357953893</v>
       </c>
       <c r="D25" t="n">
-        <v>113.0087570598105</v>
+        <v>113.0077729640267</v>
       </c>
       <c r="E25" t="n">
-        <v>1.675235959324766</v>
+        <v>1.676110978878697</v>
       </c>
       <c r="F25" t="n">
-        <v>112.0740692615903</v>
+        <v>112.0738016663776</v>
       </c>
       <c r="G25" t="n">
-        <v>0.639806142182934</v>
+        <v>0.6396322584298275</v>
       </c>
     </row>
     <row r="26">
@@ -1009,16 +1009,16 @@
         <v>8.182505792703722</v>
       </c>
       <c r="D26" t="n">
-        <v>113.8796784177052</v>
+        <v>113.8780691602877</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7706671416921154</v>
+        <v>0.7701206504954854</v>
       </c>
       <c r="F26" t="n">
-        <v>112.8280819377706</v>
+        <v>112.8276591891116</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6727806718789964</v>
+        <v>0.6726438396174217</v>
       </c>
     </row>
     <row r="27">
@@ -1032,16 +1032,16 @@
         <v>8.293138725531037</v>
       </c>
       <c r="D27" t="n">
-        <v>114.5941914175268</v>
+        <v>114.5972168343005</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6274280097638041</v>
+        <v>0.6315067328728645</v>
       </c>
       <c r="F27" t="n">
-        <v>113.6176374009706</v>
+        <v>113.6171373350177</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6997863028775981</v>
+        <v>0.6997203979769893</v>
       </c>
     </row>
     <row r="28">
@@ -1055,16 +1055,16 @@
         <v>7.167998171886779</v>
       </c>
       <c r="D28" t="n">
-        <v>114.4158610887212</v>
+        <v>114.414444929372</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1556189948195907</v>
+        <v>-0.1594907014127926</v>
       </c>
       <c r="F28" t="n">
-        <v>114.4339053600665</v>
+        <v>114.4333218596614</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7184341954015423</v>
+        <v>0.7183639227214371</v>
       </c>
     </row>
     <row r="29">
@@ -1078,16 +1078,16 @@
         <v>4.755165611073451</v>
       </c>
       <c r="D29" t="n">
-        <v>115.871476133569</v>
+        <v>115.8751425170346</v>
       </c>
       <c r="E29" t="n">
-        <v>1.272214386184672</v>
+        <v>1.276672354233128</v>
       </c>
       <c r="F29" t="n">
-        <v>115.2687207488564</v>
+        <v>115.26804721758</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7295175203215365</v>
+        <v>0.7294425647647955</v>
       </c>
     </row>
     <row r="30">
@@ -1101,16 +1101,16 @@
         <v>5.296833557133866</v>
       </c>
       <c r="D30" t="n">
-        <v>115.0134929658707</v>
+        <v>115.0132203846861</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7404610662845243</v>
+        <v>-0.7438369555591038</v>
       </c>
       <c r="F30" t="n">
-        <v>116.1166773773288</v>
+        <v>116.1158779471728</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7356346309420161</v>
+        <v>0.7355297066778803</v>
       </c>
     </row>
     <row r="31">
@@ -1124,16 +1124,16 @@
         <v>6.687017913574195</v>
       </c>
       <c r="D31" t="n">
-        <v>116.3226145528236</v>
+        <v>116.3192207505512</v>
       </c>
       <c r="E31" t="n">
-        <v>1.138233048309644</v>
+        <v>1.135521952604151</v>
       </c>
       <c r="F31" t="n">
-        <v>116.9722161151241</v>
+        <v>116.9712599442594</v>
       </c>
       <c r="G31" t="n">
-        <v>0.736792299882211</v>
+        <v>0.7366623860655181</v>
       </c>
     </row>
     <row r="32">
@@ -1147,16 +1147,16 @@
         <v>8.79753891430471</v>
       </c>
       <c r="D32" t="n">
-        <v>118.0903412342196</v>
+        <v>118.0959095268594</v>
       </c>
       <c r="E32" t="n">
-        <v>1.51967584995549</v>
+        <v>1.527424930156968</v>
       </c>
       <c r="F32" t="n">
-        <v>117.8318488072001</v>
+        <v>117.8306990972076</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7349033134757263</v>
+        <v>0.7347438621741134</v>
       </c>
     </row>
     <row r="33">
@@ -1170,16 +1170,16 @@
         <v>9.906092177036726</v>
       </c>
       <c r="D33" t="n">
-        <v>118.7653972369785</v>
+        <v>118.7643205234994</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5716437057455437</v>
+        <v>0.5659899646972804</v>
       </c>
       <c r="F33" t="n">
-        <v>118.6972525335838</v>
+        <v>118.6959242400613</v>
       </c>
       <c r="G33" t="n">
-        <v>0.734439572275349</v>
+        <v>0.7342951790008385</v>
       </c>
     </row>
     <row r="34">
@@ -1193,16 +1193,16 @@
         <v>9.448130341074162</v>
       </c>
       <c r="D34" t="n">
-        <v>119.8323490613603</v>
+        <v>119.8278574822101</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8983692634420066</v>
+        <v>0.8955020784211456</v>
       </c>
       <c r="F34" t="n">
-        <v>119.5719288140589</v>
+        <v>119.5705048837922</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7368968209501077</v>
+        <v>0.7368244944637041</v>
       </c>
     </row>
     <row r="35">
@@ -1216,16 +1216,16 @@
         <v>11.5037012486698</v>
       </c>
       <c r="D35" t="n">
-        <v>120.48481916522</v>
+        <v>120.4819876205674</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5444857828211411</v>
+        <v>0.5458915415009926</v>
       </c>
       <c r="F35" t="n">
-        <v>120.4576734876065</v>
+        <v>120.4562993917941</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7407630556207039</v>
+        <v>0.7408135550341512</v>
       </c>
     </row>
     <row r="36">
@@ -1239,16 +1239,16 @@
         <v>9.385810676011317</v>
       </c>
       <c r="D36" t="n">
-        <v>120.7969658212205</v>
+        <v>120.7981969658278</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2590755069088431</v>
+        <v>0.262453626060875</v>
       </c>
       <c r="F36" t="n">
-        <v>121.3579541805682</v>
+        <v>121.356836249686</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7473834309561909</v>
+        <v>0.7476046188027254</v>
       </c>
     </row>
     <row r="37">
@@ -1262,16 +1262,16 @@
         <v>8.234909015029217</v>
       </c>
       <c r="D37" t="n">
-        <v>123.2662282491659</v>
+        <v>123.2678286492233</v>
       </c>
       <c r="E37" t="n">
-        <v>2.04414275736022</v>
+        <v>2.044427603579351</v>
       </c>
       <c r="F37" t="n">
-        <v>122.2704241298437</v>
+        <v>122.2698088803938</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7518831010597324</v>
+        <v>0.7523042450031028</v>
       </c>
     </row>
     <row r="38">
@@ -1285,16 +1285,16 @@
         <v>7.669899792630616</v>
       </c>
       <c r="D38" t="n">
-        <v>122.2246041157597</v>
+        <v>122.2210882557368</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8450198794925967</v>
+        <v>-0.8491594319107776</v>
       </c>
       <c r="F38" t="n">
-        <v>123.1915437741775</v>
+        <v>123.1915876403791</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7533462412427951</v>
+        <v>0.7538890985647697</v>
       </c>
     </row>
     <row r="39">
@@ -1308,16 +1308,16 @@
         <v>8.313094293619102</v>
       </c>
       <c r="D39" t="n">
-        <v>124.4423395717341</v>
+        <v>124.4463164171922</v>
       </c>
       <c r="E39" t="n">
-        <v>1.814475466718562</v>
+        <v>1.820658114906749</v>
       </c>
       <c r="F39" t="n">
-        <v>124.1194897085785</v>
+        <v>124.1202217118585</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7532545708672984</v>
+        <v>0.753812893612718</v>
       </c>
     </row>
     <row r="40">
@@ -1331,16 +1331,16 @@
         <v>9.018166769196398</v>
       </c>
       <c r="D40" t="n">
-        <v>126.4953687368161</v>
+        <v>126.4949077513946</v>
       </c>
       <c r="E40" t="n">
-        <v>1.649783483778549</v>
+        <v>1.646164702324086</v>
       </c>
       <c r="F40" t="n">
-        <v>125.0519362382504</v>
+        <v>125.0532551567224</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7512490841375694</v>
+        <v>0.7517175138712417</v>
       </c>
     </row>
     <row r="41">
@@ -1354,16 +1354,16 @@
         <v>9.317917411783199</v>
       </c>
       <c r="D41" t="n">
-        <v>125.3747386291432</v>
+        <v>125.3729455249969</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.8859060366110896</v>
+        <v>-0.8869623657916179</v>
       </c>
       <c r="F41" t="n">
-        <v>125.9860302921735</v>
+        <v>125.9877313965291</v>
       </c>
       <c r="G41" t="n">
-        <v>0.74696488676787</v>
+        <v>0.7472626271387952</v>
       </c>
     </row>
     <row r="42">
@@ -1377,16 +1377,16 @@
         <v>10.67465445537125</v>
       </c>
       <c r="D42" t="n">
-        <v>127.2171792936006</v>
+        <v>127.2186638922549</v>
       </c>
       <c r="E42" t="n">
-        <v>1.469546963449517</v>
+        <v>1.4721823432712</v>
       </c>
       <c r="F42" t="n">
-        <v>126.9166782915358</v>
+        <v>126.9184800735215</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7386914225363341</v>
+        <v>0.7387613592811277</v>
       </c>
     </row>
     <row r="43">
@@ -1400,16 +1400,16 @@
         <v>9.516435003605835</v>
       </c>
       <c r="D43" t="n">
-        <v>128.5448445513741</v>
+        <v>128.5451530568809</v>
       </c>
       <c r="E43" t="n">
-        <v>1.043621046422857</v>
+        <v>1.042684401833839</v>
       </c>
       <c r="F43" t="n">
-        <v>127.8450530494741</v>
+        <v>127.8467153375288</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7314836556041797</v>
+        <v>0.7313633628999838</v>
       </c>
     </row>
     <row r="44">
@@ -1423,16 +1423,16 @@
         <v>8.835801798541866</v>
       </c>
       <c r="D44" t="n">
-        <v>127.5539261220127</v>
+        <v>127.5555041659654</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.7708737233451615</v>
+        <v>-0.7698842526389171</v>
       </c>
       <c r="F44" t="n">
-        <v>128.770128357447</v>
+        <v>128.7714617884385</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7235910079484285</v>
+        <v>0.7233243720562399</v>
       </c>
     </row>
     <row r="45">
@@ -1446,16 +1446,16 @@
         <v>8.84892556817934</v>
       </c>
       <c r="D45" t="n">
-        <v>128.9257366636258</v>
+        <v>128.9204785853389</v>
       </c>
       <c r="E45" t="n">
-        <v>1.075474964448333</v>
+        <v>1.070102327844296</v>
       </c>
       <c r="F45" t="n">
-        <v>129.6889680916321</v>
+        <v>129.6898638290247</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7135503753125789</v>
+        <v>0.7132030869503581</v>
       </c>
     </row>
     <row r="46">
@@ -1469,16 +1469,16 @@
         <v>7.585187128300092</v>
       </c>
       <c r="D46" t="n">
-        <v>129.6096887576515</v>
+        <v>129.6133687920019</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5305008229738775</v>
+        <v>0.5374555030094825</v>
       </c>
       <c r="F46" t="n">
-        <v>130.5953511866392</v>
+        <v>130.5958166077283</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6988898966076675</v>
+        <v>0.6985532654255593</v>
       </c>
     </row>
     <row r="47">
@@ -1492,16 +1492,16 @@
         <v>10.24908120617044</v>
       </c>
       <c r="D47" t="n">
-        <v>131.2594750274315</v>
+        <v>131.2565752311962</v>
       </c>
       <c r="E47" t="n">
-        <v>1.272888073101399</v>
+        <v>1.267775426646935</v>
       </c>
       <c r="F47" t="n">
-        <v>131.4767673741478</v>
+        <v>131.4768709687293</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6749215645883879</v>
+        <v>0.6746421010157064</v>
       </c>
     </row>
     <row r="48">
@@ -1515,16 +1515,16 @@
         <v>9.813975273371426</v>
       </c>
       <c r="D48" t="n">
-        <v>132.8429096413998</v>
+        <v>132.8345514234846</v>
       </c>
       <c r="E48" t="n">
-        <v>1.206339286087669</v>
+        <v>1.20220734809584</v>
       </c>
       <c r="F48" t="n">
-        <v>132.3147392537275</v>
+        <v>132.3145598548656</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6373535768452712</v>
+        <v>0.637137832657686</v>
       </c>
     </row>
     <row r="49">
@@ -1538,16 +1538,16 @@
         <v>7.771329248497366</v>
       </c>
       <c r="D49" t="n">
-        <v>133.9705910290607</v>
+        <v>133.9818490432291</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8488833846721491</v>
+        <v>0.8637042150930085</v>
       </c>
       <c r="F49" t="n">
-        <v>133.0824622464249</v>
+        <v>133.0820672353109</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5802248464740671</v>
+        <v>0.5800626788821717</v>
       </c>
     </row>
     <row r="50">
@@ -1561,16 +1561,16 @@
         <v>10.04790789483583</v>
       </c>
       <c r="D50" t="n">
-        <v>135.3936546117934</v>
+        <v>135.3934412212915</v>
       </c>
       <c r="E50" t="n">
-        <v>1.062220873851345</v>
+        <v>1.053569709735001</v>
       </c>
       <c r="F50" t="n">
-        <v>133.7472555241629</v>
+        <v>133.7466910214236</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4995348496836129</v>
+        <v>0.4994089736655098</v>
       </c>
     </row>
     <row r="51">
@@ -1584,16 +1584,16 @@
         <v>8.942137446255074</v>
       </c>
       <c r="D51" t="n">
-        <v>133.2696350850632</v>
+        <v>133.2738164851548</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.568773317198904</v>
+        <v>-1.565529849169195</v>
       </c>
       <c r="F51" t="n">
-        <v>134.2718250064923</v>
+        <v>134.2711031029602</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3922095300375332</v>
+        <v>0.3920934996833694</v>
       </c>
     </row>
     <row r="52">
@@ -1607,16 +1607,16 @@
         <v>2.360223575229114</v>
       </c>
       <c r="D52" t="n">
-        <v>133.3338034046139</v>
+        <v>133.3298353950439</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04814924233103568</v>
+        <v>0.04203294492978671</v>
       </c>
       <c r="F52" t="n">
-        <v>134.6160646661207</v>
+        <v>134.6152480483554</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2563751997947179</v>
+        <v>0.2563060386353158</v>
       </c>
     </row>
     <row r="53">
@@ -1630,16 +1630,16 @@
         <v>8.854445098099134</v>
       </c>
       <c r="D53" t="n">
-        <v>135.5667849327847</v>
+        <v>135.5714769093224</v>
       </c>
       <c r="E53" t="n">
-        <v>1.674730241808646</v>
+        <v>1.681275243186775</v>
       </c>
       <c r="F53" t="n">
-        <v>134.7449738537922</v>
+        <v>134.7440744247718</v>
       </c>
       <c r="G53" t="n">
-        <v>0.09576062707765232</v>
+        <v>0.09569969099646869</v>
       </c>
     </row>
     <row r="54">
@@ -1653,16 +1653,16 @@
         <v>4.436248124025653</v>
       </c>
       <c r="D54" t="n">
-        <v>135.0176708125861</v>
+        <v>135.0130805791248</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.405050632771804</v>
+        <v>-0.4118833422247974</v>
       </c>
       <c r="F54" t="n">
-        <v>134.6301986535778</v>
+        <v>134.6291285254742</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.08517957808133758</v>
+        <v>-0.08530683058852162</v>
       </c>
     </row>
     <row r="55">
@@ -1676,16 +1676,16 @@
         <v>3.219560797138683</v>
       </c>
       <c r="D55" t="n">
-        <v>133.4328661058711</v>
+        <v>133.4327643628135</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.173775771109845</v>
+        <v>-1.170491192062798</v>
       </c>
       <c r="F55" t="n">
-        <v>134.2551213182752</v>
+        <v>134.2537332538157</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2785982187159277</v>
+        <v>-0.2788365903946612</v>
       </c>
     </row>
     <row r="56">
@@ -1699,16 +1699,16 @@
         <v>7.262197929018328</v>
       </c>
       <c r="D56" t="n">
-        <v>135.2642376463917</v>
+        <v>135.267249978732</v>
       </c>
       <c r="E56" t="n">
-        <v>1.372504086862307</v>
+        <v>1.37483894954795</v>
       </c>
       <c r="F56" t="n">
-        <v>133.6212648575117</v>
+        <v>133.6194025747785</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.4721283289155167</v>
+        <v>-0.4724864356940799</v>
       </c>
     </row>
     <row r="57">
@@ -1722,16 +1722,16 @@
         <v>3.748714579465997</v>
       </c>
       <c r="D57" t="n">
-        <v>135.8106360277523</v>
+        <v>135.8095634411895</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4039488861712641</v>
+        <v>0.4009200028409055</v>
       </c>
       <c r="F57" t="n">
-        <v>132.748383875475</v>
+        <v>132.7459818349497</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.6532500519041946</v>
+        <v>-0.6536631080505089</v>
       </c>
     </row>
     <row r="58">
@@ -1745,16 +1745,16 @@
         <v>7.024081170157487</v>
       </c>
       <c r="D58" t="n">
-        <v>135.7778228136011</v>
+        <v>135.7758830678433</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.02416100469814353</v>
+        <v>-0.02479970665747544</v>
       </c>
       <c r="F58" t="n">
-        <v>131.6749265957806</v>
+        <v>131.6720179605757</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.8086405637158691</v>
+        <v>-0.809036823208146</v>
       </c>
     </row>
     <row r="59">
@@ -1768,16 +1768,16 @@
         <v>1.541712636359279</v>
       </c>
       <c r="D59" t="n">
-        <v>132.7700769639304</v>
+        <v>132.7654490215131</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.215196699537444</v>
+        <v>-2.217208224545999</v>
       </c>
       <c r="F59" t="n">
-        <v>130.4574055905078</v>
+        <v>130.4541360617579</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.9246414915501617</v>
+        <v>-0.9249360021067616</v>
       </c>
     </row>
     <row r="60">
@@ -1791,16 +1791,16 @@
         <v>-3.243167427709196</v>
       </c>
       <c r="D60" t="n">
-        <v>130.371407837739</v>
+        <v>130.3718244621423</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.806633829731851</v>
+        <v>-1.802897197284366</v>
       </c>
       <c r="F60" t="n">
-        <v>129.1664986461348</v>
+        <v>129.1630997520439</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.9895236981984823</v>
+        <v>-0.9896476636837406</v>
       </c>
     </row>
     <row r="61">
@@ -1814,16 +1814,16 @@
         <v>-4.214127138728699</v>
       </c>
       <c r="D61" t="n">
-        <v>124.8717711724246</v>
+        <v>124.8759824904546</v>
       </c>
       <c r="E61" t="n">
-        <v>-4.218437736101805</v>
+        <v>-4.215513585363311</v>
       </c>
       <c r="F61" t="n">
-        <v>127.8796651446959</v>
+        <v>127.8763984869822</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.9962594906008775</v>
+        <v>-0.9961833275384748</v>
       </c>
     </row>
     <row r="62">
@@ -1837,16 +1837,16 @@
         <v>-7.50115377191743</v>
       </c>
       <c r="D62" t="n">
-        <v>124.641143373885</v>
+        <v>124.6329197081702</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1846917012341578</v>
+        <v>-0.1946433392850224</v>
       </c>
       <c r="F62" t="n">
-        <v>126.6833216387893</v>
+        <v>126.680357845696</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.9355228640557272</v>
+        <v>-0.9353099207027782</v>
       </c>
     </row>
     <row r="63">
@@ -1860,16 +1860,16 @@
         <v>-6.485690385895808</v>
       </c>
       <c r="D63" t="n">
-        <v>126.0508982685594</v>
+        <v>126.06046487384</v>
       </c>
       <c r="E63" t="n">
-        <v>1.131050996897159</v>
+        <v>1.145399761966885</v>
       </c>
       <c r="F63" t="n">
-        <v>125.657475895857</v>
+        <v>125.6549214272675</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.8097717439532204</v>
+        <v>-0.8094675732424861</v>
       </c>
     </row>
     <row r="64">
@@ -1883,16 +1883,16 @@
         <v>-4.661325693995892</v>
       </c>
       <c r="D64" t="n">
-        <v>123.292752018933</v>
+        <v>123.2914090793804</v>
       </c>
       <c r="E64" t="n">
-        <v>-2.188121058645734</v>
+        <v>-2.196609220211016</v>
       </c>
       <c r="F64" t="n">
-        <v>124.8716570042342</v>
+        <v>124.8694076572488</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.6253658097303543</v>
+        <v>-0.6251356979069271</v>
       </c>
     </row>
     <row r="65">
@@ -1906,16 +1906,16 @@
         <v>-11.90107402568657</v>
       </c>
       <c r="D65" t="n">
-        <v>121.794513409679</v>
+        <v>121.7946165075425</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.215187904171273</v>
+        <v>-1.214028279029662</v>
       </c>
       <c r="F65" t="n">
-        <v>124.3752026841051</v>
+        <v>124.3730739864755</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.397571660406669</v>
+        <v>-0.397482201673995</v>
       </c>
     </row>
     <row r="66">
@@ -1929,16 +1929,16 @@
         <v>-13.70071289959009</v>
       </c>
       <c r="D66" t="n">
-        <v>121.1917358132491</v>
+        <v>121.1916381600791</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4949135881042395</v>
+        <v>-0.4950779966748939</v>
       </c>
       <c r="F66" t="n">
-        <v>124.1960929617909</v>
+        <v>124.193894372947</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.1440075822582827</v>
+        <v>-0.1440662418201697</v>
       </c>
     </row>
     <row r="67">
@@ -1952,16 +1952,16 @@
         <v>-7.964803315040299</v>
       </c>
       <c r="D67" t="n">
-        <v>122.4408740245202</v>
+        <v>122.4408685798386</v>
       </c>
       <c r="E67" t="n">
-        <v>1.030712369031477</v>
+        <v>1.030789284413643</v>
       </c>
       <c r="F67" t="n">
-        <v>124.3424413100584</v>
+        <v>124.3400211187705</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1178365154469674</v>
+        <v>0.1176601688523533</v>
       </c>
     </row>
     <row r="68">
@@ -1975,16 +1975,16 @@
         <v>-6.788435845530998</v>
       </c>
       <c r="D68" t="n">
-        <v>124.8630727732574</v>
+        <v>124.8620885214533</v>
       </c>
       <c r="E68" t="n">
-        <v>1.9782599299742</v>
+        <v>1.977460605840079</v>
       </c>
       <c r="F68" t="n">
-        <v>124.7991192917344</v>
+        <v>124.7963317256284</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3672744212390739</v>
+        <v>0.3669861101455894</v>
       </c>
     </row>
     <row r="69">
@@ -1998,16 +1998,16 @@
         <v>-5.586709112728727</v>
       </c>
       <c r="D69" t="n">
-        <v>126.7377173461809</v>
+        <v>126.7414982928567</v>
       </c>
       <c r="E69" t="n">
-        <v>1.501360275129286</v>
+        <v>1.505188479272078</v>
       </c>
       <c r="F69" t="n">
-        <v>125.532529169593</v>
+        <v>125.5292841850519</v>
       </c>
       <c r="G69" t="n">
-        <v>0.587672318539461</v>
+        <v>0.5873189133754693</v>
       </c>
     </row>
     <row r="70">
@@ -2021,16 +2021,16 @@
         <v>-4.539673760848757</v>
       </c>
       <c r="D70" t="n">
-        <v>128.1044966726025</v>
+        <v>128.1016999777463</v>
       </c>
       <c r="E70" t="n">
-        <v>1.078431389677206</v>
+        <v>1.073209409081329</v>
       </c>
       <c r="F70" t="n">
-        <v>126.4992111000773</v>
+        <v>126.495433064716</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7700648882636614</v>
+        <v>0.7696601521600854</v>
       </c>
     </row>
     <row r="71">
@@ -2044,16 +2044,16 @@
         <v>-2.542514983523148</v>
       </c>
       <c r="D71" t="n">
-        <v>129.3673663814277</v>
+        <v>129.3658165109555</v>
       </c>
       <c r="E71" t="n">
-        <v>0.985812162435451</v>
+        <v>0.9868069927477734</v>
       </c>
       <c r="F71" t="n">
-        <v>127.6479016105108</v>
+        <v>127.6435570887088</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9080614024736349</v>
+        <v>0.9076406919808875</v>
       </c>
     </row>
     <row r="72">
@@ -2067,16 +2067,16 @@
         <v>1.246442173040819</v>
       </c>
       <c r="D72" t="n">
-        <v>129.7532779548078</v>
+        <v>129.7522874890063</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2983067400802213</v>
+        <v>0.2987427347301121</v>
       </c>
       <c r="F72" t="n">
-        <v>128.924335279801</v>
+        <v>128.919463174992</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9999644750799916</v>
+        <v>0.9995851850136432</v>
       </c>
     </row>
     <row r="73">
@@ -2090,16 +2090,16 @@
         <v>2.284481459767946</v>
       </c>
       <c r="D73" t="n">
-        <v>127.8940133256334</v>
+        <v>127.8965536619235</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.432923050947451</v>
+        <v>-1.430212802406288</v>
       </c>
       <c r="F73" t="n">
-        <v>130.2764109794571</v>
+        <v>130.2711324353449</v>
       </c>
       <c r="G73" t="n">
-        <v>1.048735831541634</v>
+        <v>1.048460199154107</v>
       </c>
     </row>
     <row r="74">
@@ -2113,16 +2113,16 @@
         <v>4.065881809302923</v>
       </c>
       <c r="D74" t="n">
-        <v>131.9843880951992</v>
+        <v>131.9724398812948</v>
       </c>
       <c r="E74" t="n">
-        <v>3.198253509451732</v>
+        <v>3.186861649255519</v>
       </c>
       <c r="F74" t="n">
-        <v>131.655569583904</v>
+        <v>131.6501073295117</v>
       </c>
       <c r="G74" t="n">
-        <v>1.058640312607608</v>
+        <v>1.058542186889497</v>
       </c>
     </row>
     <row r="75">
@@ -2136,16 +2136,16 @@
         <v>4.321774168656518</v>
       </c>
       <c r="D75" t="n">
-        <v>132.9869536195466</v>
+        <v>133.0022306548703</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7596091771280555</v>
+        <v>0.7803074448738698</v>
       </c>
       <c r="F75" t="n">
-        <v>133.0202095393875</v>
+        <v>133.0148600267148</v>
       </c>
       <c r="G75" t="n">
-        <v>1.0365227690681</v>
+        <v>1.036651412510551</v>
       </c>
     </row>
     <row r="76">
@@ -2159,16 +2159,16 @@
         <v>8.504615194797509</v>
       </c>
       <c r="D76" t="n">
-        <v>133.8499744629016</v>
+        <v>133.8466456415002</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6489515098029273</v>
+        <v>0.6348878379499752</v>
       </c>
       <c r="F76" t="n">
-        <v>134.3393094209298</v>
+        <v>134.3346938119614</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9916537390145521</v>
+        <v>0.9922453664061379</v>
       </c>
     </row>
     <row r="77">
@@ -2182,16 +2182,16 @@
         <v>13.89444094540704</v>
       </c>
       <c r="D77" t="n">
-        <v>136.9299606339092</v>
+        <v>136.9274071133927</v>
       </c>
       <c r="E77" t="n">
-        <v>2.301073409514373</v>
+        <v>2.301709883820394</v>
       </c>
       <c r="F77" t="n">
-        <v>135.5921686044786</v>
+        <v>135.5886465049505</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9326080273519324</v>
+        <v>0.9334540894880803</v>
       </c>
     </row>
     <row r="78">
@@ -2205,16 +2205,16 @@
         <v>18.84829907811478</v>
       </c>
       <c r="D78" t="n">
-        <v>139.1671086793744</v>
+        <v>139.1716767437787</v>
       </c>
       <c r="E78" t="n">
-        <v>1.633790030398387</v>
+        <v>1.639021491532006</v>
       </c>
       <c r="F78" t="n">
-        <v>136.7636844740885</v>
+        <v>136.7611432961293</v>
       </c>
       <c r="G78" t="n">
-        <v>0.863999655486964</v>
+        <v>0.8647455531138633</v>
       </c>
     </row>
     <row r="79">
@@ -2228,16 +2228,16 @@
         <v>15.89086039230475</v>
       </c>
       <c r="D79" t="n">
-        <v>140.5486404290224</v>
+        <v>140.5466258851555</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9927142718979951</v>
+        <v>0.9879518401637171</v>
       </c>
       <c r="F79" t="n">
-        <v>137.8464482026693</v>
+        <v>137.84428360693</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7917041228776611</v>
+        <v>0.7919941912559807</v>
       </c>
     </row>
     <row r="80">
@@ -2251,16 +2251,16 @@
         <v>9.533869874543882</v>
       </c>
       <c r="D80" t="n">
-        <v>139.4669807514541</v>
+        <v>139.459068435407</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.7695981080048142</v>
+        <v>-0.7738054491875204</v>
       </c>
       <c r="F80" t="n">
-        <v>138.8398779384761</v>
+        <v>138.8371068598555</v>
       </c>
       <c r="G80" t="n">
-        <v>0.720678514941639</v>
+        <v>0.7202498550876442</v>
       </c>
     </row>
     <row r="81">
@@ -2274,16 +2274,16 @@
         <v>10.67930930144473</v>
       </c>
       <c r="D81" t="n">
-        <v>139.8426539535663</v>
+        <v>139.8452185011689</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2693635440360396</v>
+        <v>0.2768913273938409</v>
       </c>
       <c r="F81" t="n">
-        <v>139.7506201417289</v>
+        <v>139.7462076566574</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6559658628167711</v>
+        <v>0.654796701950616</v>
       </c>
     </row>
     <row r="82">
@@ -2297,16 +2297,16 @@
         <v>8.330061357551813</v>
       </c>
       <c r="D82" t="n">
-        <v>139.4534863528754</v>
+        <v>139.4588341213421</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.278289627440941</v>
+        <v>-0.2762943087850687</v>
       </c>
       <c r="F82" t="n">
-        <v>140.5940893859114</v>
+        <v>140.5870783978586</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6035531315188791</v>
+        <v>0.6017127443394656</v>
       </c>
     </row>
     <row r="83">
@@ -2320,16 +2320,16 @@
         <v>6.341667755090086</v>
       </c>
       <c r="D83" t="n">
-        <v>140.2729051791022</v>
+        <v>140.2722519406554</v>
       </c>
       <c r="E83" t="n">
-        <v>0.5875929298413638</v>
+        <v>0.5832673307777441</v>
       </c>
       <c r="F83" t="n">
-        <v>141.3846762683454</v>
+        <v>141.3744610480881</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5623187190067398</v>
+        <v>0.5600675817454004</v>
       </c>
     </row>
     <row r="84">
@@ -2343,16 +2343,16 @@
         <v>9.840597859112819</v>
       </c>
       <c r="D84" t="n">
-        <v>142.0915351060385</v>
+        <v>142.091236687242</v>
       </c>
       <c r="E84" t="n">
-        <v>1.296494091010842</v>
+        <v>1.296753079401711</v>
       </c>
       <c r="F84" t="n">
-        <v>142.1346055885439</v>
+        <v>142.1210446640436</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5304176803256695</v>
+        <v>0.5280894515322672</v>
       </c>
     </row>
     <row r="85">
@@ -2366,16 +2366,16 @@
         <v>9.653509716147624</v>
       </c>
       <c r="D85" t="n">
-        <v>142.0391218869364</v>
+        <v>142.0400735442028</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.03688693986097746</v>
+        <v>-0.03600724733769312</v>
       </c>
       <c r="F85" t="n">
-        <v>142.8530788985558</v>
+        <v>142.836544669122</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5054879542085331</v>
+        <v>0.5034440935680777</v>
       </c>
     </row>
     <row r="86">
@@ -2389,16 +2389,16 @@
         <v>9.523210214851389</v>
       </c>
       <c r="D86" t="n">
-        <v>145.9159532899234</v>
+        <v>145.9100295275116</v>
       </c>
       <c r="E86" t="n">
-        <v>2.729410990074243</v>
+        <v>2.724552224414651</v>
       </c>
       <c r="F86" t="n">
-        <v>143.5496330719239</v>
+        <v>143.5309543450469</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4876017925120806</v>
+        <v>0.4861568708018922</v>
       </c>
     </row>
     <row r="87">
@@ -2412,16 +2412,16 @@
         <v>8.084508608921695</v>
       </c>
       <c r="D87" t="n">
-        <v>143.7786722926512</v>
+        <v>143.8065025711078</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.464734286473529</v>
+        <v>-1.441660291081746</v>
       </c>
       <c r="F87" t="n">
-        <v>144.2248905458287</v>
+        <v>144.2052654283204</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4703999999543527</v>
+        <v>0.4698018530918375</v>
       </c>
     </row>
     <row r="88">
@@ -2435,16 +2435,16 @@
         <v>7.382519772331236</v>
       </c>
       <c r="D88" t="n">
-        <v>144.8647832527435</v>
+        <v>144.8428767367241</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7554047778947677</v>
+        <v>0.720672672714386</v>
       </c>
       <c r="F88" t="n">
-        <v>144.8707344666893</v>
+        <v>144.8515112221198</v>
       </c>
       <c r="G88" t="n">
-        <v>0.4478033704282183</v>
+        <v>0.4481429938635983</v>
       </c>
     </row>
     <row r="89">
@@ -2458,16 +2458,16 @@
         <v>3.609482349652865</v>
       </c>
       <c r="D89" t="n">
-        <v>144.9869944701244</v>
+        <v>144.9833577070741</v>
       </c>
       <c r="E89" t="n">
-        <v>0.08436226848016304</v>
+        <v>0.09698852543876058</v>
       </c>
       <c r="F89" t="n">
-        <v>145.4661877147545</v>
+        <v>145.4488486140888</v>
       </c>
       <c r="G89" t="n">
-        <v>0.4110238346325019</v>
+        <v>0.4123791232339897</v>
       </c>
     </row>
     <row r="90">
@@ -2481,16 +2481,16 @@
         <v>5.102573098650524</v>
       </c>
       <c r="D90" t="n">
-        <v>147.0298202258276</v>
+        <v>147.0298080226296</v>
       </c>
       <c r="E90" t="n">
-        <v>1.408971724097754</v>
+        <v>1.411507050133395</v>
       </c>
       <c r="F90" t="n">
-        <v>145.984659477233</v>
+        <v>145.9705034288993</v>
       </c>
       <c r="G90" t="n">
-        <v>0.3564208085903147</v>
+        <v>0.3586517320564298</v>
       </c>
     </row>
     <row r="91">
@@ -2504,16 +2504,16 @@
         <v>4.558945515147002</v>
       </c>
       <c r="D91" t="n">
-        <v>146.914540295387</v>
+        <v>146.9181892616626</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.07840581608786579</v>
+        <v>-0.07591573604574364</v>
       </c>
       <c r="F91" t="n">
-        <v>146.3966855912658</v>
+        <v>146.3866238955605</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2822393226167037</v>
+        <v>0.285071611651901</v>
       </c>
     </row>
     <row r="92">
@@ -2527,16 +2527,16 @@
         <v>4.926251981419824</v>
       </c>
       <c r="D92" t="n">
-        <v>147.2130895308167</v>
+        <v>147.1992359671853</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2032128575084613</v>
+        <v>0.1912946973653362</v>
       </c>
       <c r="F92" t="n">
-        <v>146.6752465571571</v>
+        <v>146.6696595238446</v>
       </c>
       <c r="G92" t="n">
-        <v>0.190278191590366</v>
+        <v>0.1933480127842984</v>
       </c>
     </row>
     <row r="93">
@@ -2550,16 +2550,16 @@
         <v>6.668701445199815</v>
       </c>
       <c r="D93" t="n">
-        <v>146.8201417560026</v>
+        <v>146.8328323266506</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.2669244807418494</v>
+        <v>-0.2489168086554798</v>
       </c>
       <c r="F93" t="n">
-        <v>146.799996940957</v>
+        <v>146.7987770738223</v>
       </c>
       <c r="G93" t="n">
-        <v>0.08505210437897404</v>
+        <v>0.08803289678105841</v>
       </c>
     </row>
     <row r="94">
@@ -2573,16 +2573,16 @@
         <v>7.662585153728301</v>
       </c>
       <c r="D94" t="n">
-        <v>148.3374764170985</v>
+        <v>148.3386394101092</v>
       </c>
       <c r="E94" t="n">
-        <v>1.033464920376929</v>
+        <v>1.025524781888535</v>
       </c>
       <c r="F94" t="n">
-        <v>146.7640964554814</v>
+        <v>146.7666284578797</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.02445537208699022</v>
+        <v>-0.02189978457822406</v>
       </c>
     </row>
     <row r="95">
@@ -2596,16 +2596,16 @@
         <v>7.334055546381705</v>
       </c>
       <c r="D95" t="n">
-        <v>147.2186151882167</v>
+        <v>147.2284200396229</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.7542674015403463</v>
+        <v>-0.7484357244351543</v>
       </c>
       <c r="F95" t="n">
-        <v>146.5760603853007</v>
+        <v>146.5812428556781</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.1281213012732678</v>
+        <v>-0.1263131845089589</v>
       </c>
     </row>
     <row r="96">
@@ -2619,16 +2619,16 @@
         <v>4.844469087463892</v>
       </c>
       <c r="D96" t="n">
-        <v>147.1822710985149</v>
+        <v>147.1817913291667</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.02468715634591945</v>
+        <v>-0.03167099833284226</v>
       </c>
       <c r="F96" t="n">
-        <v>146.26152590692</v>
+        <v>146.2679423489215</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.2145878921523234</v>
+        <v>-0.213738470661724</v>
       </c>
     </row>
     <row r="97">
@@ -2642,16 +2642,16 @@
         <v>3.526928972446129</v>
       </c>
       <c r="D97" t="n">
-        <v>147.9549179319426</v>
+        <v>147.9455928499123</v>
       </c>
       <c r="E97" t="n">
-        <v>0.524959173180946</v>
+        <v>0.5189510970398743</v>
       </c>
       <c r="F97" t="n">
-        <v>145.8584450937997</v>
+        <v>145.8646615869831</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.2755890933182314</v>
+        <v>-0.2757137042212179</v>
       </c>
     </row>
     <row r="98">
@@ -2665,16 +2665,16 @@
         <v>2.342375809158753</v>
       </c>
       <c r="D98" t="n">
-        <v>147.6276241622116</v>
+        <v>147.6154868243059</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.2212118220237329</v>
+        <v>-0.2231266367909654</v>
       </c>
       <c r="F98" t="n">
-        <v>145.415116890084</v>
+        <v>145.4200022028022</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.30394414490749</v>
+        <v>-0.3048438047591731</v>
       </c>
     </row>
     <row r="99">
@@ -2688,16 +2688,16 @@
         <v>2.201097667225497</v>
       </c>
       <c r="D99" t="n">
-        <v>144.7798769306095</v>
+        <v>144.7928314130222</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.929007018681745</v>
+        <v>-1.912167532017335</v>
       </c>
       <c r="F99" t="n">
-        <v>144.9858121967944</v>
+        <v>144.9887103190777</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.2952270042282521</v>
+        <v>-0.2965836041750549</v>
       </c>
     </row>
     <row r="100">
@@ -2711,16 +2711,16 @@
         <v>0.2987562282469156</v>
       </c>
       <c r="D100" t="n">
-        <v>145.424297807033</v>
+        <v>145.4234806625537</v>
       </c>
       <c r="E100" t="n">
-        <v>0.4451038984736755</v>
+        <v>0.4355528125095134</v>
       </c>
       <c r="F100" t="n">
-        <v>144.6217223497578</v>
+        <v>144.6224625245964</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.2511210176498935</v>
+        <v>-0.2526043535908968</v>
       </c>
     </row>
     <row r="101">
@@ -2734,16 +2734,16 @@
         <v>-3.651812272129661</v>
       </c>
       <c r="D101" t="n">
-        <v>141.937886824991</v>
+        <v>141.9356922216272</v>
       </c>
       <c r="E101" t="n">
-        <v>-2.397406096929018</v>
+        <v>-2.398366773395907</v>
       </c>
       <c r="F101" t="n">
-        <v>144.3652109566615</v>
+        <v>144.3635888965373</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.177367126409905</v>
+        <v>-0.1789995990526876</v>
       </c>
     </row>
     <row r="102">
@@ -2757,16 +2757,16 @@
         <v>-5.279965037429136</v>
       </c>
       <c r="D102" t="n">
-        <v>140.2035808273765</v>
+        <v>140.2080080080876</v>
       </c>
       <c r="E102" t="n">
-        <v>-1.221876721155439</v>
+        <v>-1.21723027273643</v>
       </c>
       <c r="F102" t="n">
-        <v>144.2486986812897</v>
+        <v>144.2447699773331</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.08070661525705702</v>
+        <v>-0.08230532374012967</v>
       </c>
     </row>
     <row r="103">
@@ -2780,16 +2780,16 @@
         <v>-4.888874791414139</v>
       </c>
       <c r="D103" t="n">
-        <v>140.838458907023</v>
+        <v>140.8362263297009</v>
       </c>
       <c r="E103" t="n">
-        <v>0.4528258664293645</v>
+        <v>0.4480616553493348</v>
       </c>
       <c r="F103" t="n">
-        <v>144.2898162769737</v>
+        <v>144.2838235013849</v>
       </c>
       <c r="G103" t="n">
-        <v>0.02850465623598097</v>
+        <v>0.02707448183936378</v>
       </c>
     </row>
     <row r="104">
@@ -2803,16 +2803,16 @@
         <v>0.3311365411739757</v>
       </c>
       <c r="D104" t="n">
-        <v>144.650340436018</v>
+        <v>144.6261135929174</v>
       </c>
       <c r="E104" t="n">
-        <v>2.706562936414585</v>
+        <v>2.690988932310788</v>
       </c>
       <c r="F104" t="n">
-        <v>144.4894704838075</v>
+        <v>144.4817849449065</v>
       </c>
       <c r="G104" t="n">
-        <v>0.1383702689388429</v>
+        <v>0.1372027984271966</v>
       </c>
     </row>
     <row r="105">
@@ -2826,16 +2826,16 @@
         <v>-0.4817319644454443</v>
       </c>
       <c r="D105" t="n">
-        <v>145.190912823251</v>
+        <v>145.2020973049518</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3737097234638469</v>
+        <v>0.3982570627982795</v>
       </c>
       <c r="F105" t="n">
-        <v>144.8333785566793</v>
+        <v>144.8244522882019</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2380160102464686</v>
+        <v>0.2371699265938361</v>
       </c>
     </row>
     <row r="106">
@@ -2849,16 +2849,16 @@
         <v>-3.193138104166053</v>
       </c>
       <c r="D106" t="n">
-        <v>146.2022351933019</v>
+        <v>146.2152775547291</v>
       </c>
       <c r="E106" t="n">
-        <v>0.6965466022533633</v>
+        <v>0.697772462369727</v>
       </c>
       <c r="F106" t="n">
-        <v>145.2929527870714</v>
+        <v>145.2831914856655</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3173123729984866</v>
+        <v>0.3167553477438503</v>
       </c>
     </row>
     <row r="107">
@@ -2872,16 +2872,16 @@
         <v>1.503826605302748</v>
       </c>
       <c r="D107" t="n">
-        <v>146.9432815304483</v>
+        <v>146.9454243474299</v>
       </c>
       <c r="E107" t="n">
-        <v>0.5068638903957634</v>
+        <v>0.4993642284935049</v>
       </c>
       <c r="F107" t="n">
-        <v>145.8277643078104</v>
+        <v>145.8176135707443</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3680918519997078</v>
+        <v>0.3678485305931076</v>
       </c>
     </row>
     <row r="108">
@@ -2895,16 +2895,16 @@
         <v>0.008053148426128587</v>
       </c>
       <c r="D108" t="n">
-        <v>147.0945470582242</v>
+        <v>147.0897903048377</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1029414384927918</v>
+        <v>0.09824460887361397</v>
       </c>
       <c r="F108" t="n">
-        <v>146.3955335540477</v>
+        <v>146.3853969113791</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3893423511855332</v>
+        <v>0.3893791200741106</v>
       </c>
     </row>
     <row r="109">
@@ -2918,16 +2918,16 @@
         <v>0.1558298426389939</v>
       </c>
       <c r="D109" t="n">
-        <v>149.2775313451495</v>
+        <v>149.2801452815835</v>
       </c>
       <c r="E109" t="n">
-        <v>1.484068805121126</v>
+        <v>1.489127812478614</v>
       </c>
       <c r="F109" t="n">
-        <v>146.9574914788795</v>
+        <v>146.9477495734007</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3838627526326519</v>
+        <v>0.3841589898219553</v>
       </c>
     </row>
     <row r="110">
@@ -2941,16 +2941,16 @@
         <v>0.2371546019941633</v>
       </c>
       <c r="D110" t="n">
-        <v>145.8457417790087</v>
+        <v>145.8444622040475</v>
       </c>
       <c r="E110" t="n">
-        <v>-2.298932421521656</v>
+        <v>-2.301500357636584</v>
       </c>
       <c r="F110" t="n">
-        <v>147.4846931194585</v>
+        <v>147.4756282848695</v>
       </c>
       <c r="G110" t="n">
-        <v>0.3587443112111259</v>
+        <v>0.3592288503915313</v>
       </c>
     </row>
     <row r="111">
@@ -2964,16 +2964,16 @@
         <v>0.328493726602801</v>
       </c>
       <c r="D111" t="n">
-        <v>148.7130257249416</v>
+        <v>148.7193750865648</v>
       </c>
       <c r="E111" t="n">
-        <v>1.965970285424959</v>
+        <v>1.971218405601945</v>
       </c>
       <c r="F111" t="n">
-        <v>147.9513629818847</v>
+        <v>147.9431114652407</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3164191839543804</v>
+        <v>0.3169901263063508</v>
       </c>
     </row>
     <row r="112">
@@ -2987,16 +2987,16 @@
         <v>1.33133199458284</v>
       </c>
       <c r="D112" t="n">
-        <v>148.7946696285144</v>
+        <v>148.7895998418822</v>
       </c>
       <c r="E112" t="n">
-        <v>0.05490030424351744</v>
+        <v>0.04721964120444966</v>
       </c>
       <c r="F112" t="n">
-        <v>148.3359418579508</v>
+        <v>148.3284856047954</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2599360143192229</v>
+        <v>0.2604880590504308</v>
       </c>
     </row>
     <row r="113">
@@ -3010,16 +3010,16 @@
         <v>7.161419455382685</v>
       </c>
       <c r="D113" t="n">
-        <v>148.4149110931584</v>
+        <v>148.4199531126731</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.2552232121648643</v>
+        <v>-0.2484358648735281</v>
       </c>
       <c r="F113" t="n">
-        <v>148.6241951906047</v>
+        <v>148.6175251554408</v>
       </c>
       <c r="G113" t="n">
-        <v>0.194324672121553</v>
+        <v>0.1948644924586915</v>
       </c>
     </row>
     <row r="114">
@@ -3033,16 +3033,16 @@
         <v>6.714748714693712</v>
       </c>
       <c r="D114" t="n">
-        <v>148.500264150766</v>
+        <v>148.4978509585143</v>
       </c>
       <c r="E114" t="n">
-        <v>0.05750975894467558</v>
+        <v>0.05248475303187661</v>
       </c>
       <c r="F114" t="n">
-        <v>148.8076599745299</v>
+        <v>148.8017928922079</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1234420705793724</v>
+        <v>0.1239878921239495</v>
       </c>
     </row>
     <row r="115">
@@ -3056,16 +3056,16 @@
         <v>4.857150930999921</v>
       </c>
       <c r="D115" t="n">
-        <v>149.1481460981537</v>
+        <v>149.1455172709197</v>
       </c>
       <c r="E115" t="n">
-        <v>0.4362833635972407</v>
+        <v>0.4361452426583128</v>
       </c>
       <c r="F115" t="n">
-        <v>148.8805415801065</v>
+        <v>148.875549433977</v>
       </c>
       <c r="G115" t="n">
-        <v>0.04897705238364836</v>
+        <v>0.04956697116047337</v>
       </c>
     </row>
     <row r="116">
@@ -3079,16 +3079,16 @@
         <v>2.633888016064148</v>
       </c>
       <c r="D116" t="n">
-        <v>148.0489835491009</v>
+        <v>148.030735209357</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.7369602491267386</v>
+        <v>-0.7474459051543363</v>
       </c>
       <c r="F116" t="n">
-        <v>148.8389846867813</v>
+        <v>148.8349982462062</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.02791291117304695</v>
+        <v>-0.02723831275517341</v>
       </c>
     </row>
     <row r="117">
@@ -3102,16 +3102,16 @@
         <v>1.872559237178635</v>
       </c>
       <c r="D117" t="n">
-        <v>150.2433081896353</v>
+        <v>150.2535682042782</v>
       </c>
       <c r="E117" t="n">
-        <v>1.482161233350652</v>
+        <v>1.501602347497325</v>
       </c>
       <c r="F117" t="n">
-        <v>148.6845249740588</v>
+        <v>148.6817211834727</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.1037763816029127</v>
+        <v>-0.102984556414583</v>
       </c>
     </row>
     <row r="118">
@@ -3125,16 +3125,16 @@
         <v>3.181904106346337</v>
       </c>
       <c r="D118" t="n">
-        <v>150.1989754284783</v>
+        <v>150.2069637536086</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.02950731163421949</v>
+        <v>-0.03101720060737989</v>
       </c>
       <c r="F118" t="n">
-        <v>148.4255900533358</v>
+        <v>148.4239446950601</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.1741505518265996</v>
+        <v>-0.1733747002393642</v>
       </c>
     </row>
     <row r="119">
@@ -3148,16 +3148,16 @@
         <v>0.9934412121033205</v>
       </c>
       <c r="D119" t="n">
-        <v>148.8205306701404</v>
+        <v>148.8229414786125</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.9177457798267312</v>
+        <v>-0.9214101932493151</v>
       </c>
       <c r="F119" t="n">
-        <v>148.0722536379042</v>
+        <v>148.0715313208886</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.2380562646269908</v>
+        <v>-0.2374370084932025</v>
       </c>
     </row>
     <row r="120">
@@ -3171,16 +3171,16 @@
         <v>-0.4628805978500168</v>
       </c>
       <c r="D120" t="n">
-        <v>148.1875159072461</v>
+        <v>148.1843143787314</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.4253544588531355</v>
+        <v>-0.4291187188857748</v>
       </c>
       <c r="F120" t="n">
-        <v>147.6355547177216</v>
+        <v>147.6354437580278</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.2949228565471032</v>
+        <v>-0.2945114155101862</v>
       </c>
     </row>
     <row r="121">
@@ -3194,16 +3194,16 @@
         <v>-0.7021475533727397</v>
       </c>
       <c r="D121" t="n">
-        <v>147.1112383765556</v>
+        <v>147.1120290966267</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.7262943332987106</v>
+        <v>-0.72361591481544</v>
       </c>
       <c r="F121" t="n">
-        <v>147.1321364779713</v>
+        <v>147.1323152070563</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.3409871292270452</v>
+        <v>-0.3407911665142649</v>
       </c>
     </row>
     <row r="122">
@@ -3217,16 +3217,16 @@
         <v>1.064061476643502</v>
       </c>
       <c r="D122" t="n">
-        <v>145.6311783686547</v>
+        <v>145.6235825739701</v>
       </c>
       <c r="E122" t="n">
-        <v>-1.006082216582584</v>
+        <v>-1.011777576447543</v>
       </c>
       <c r="F122" t="n">
-        <v>146.5839804030072</v>
+        <v>146.5841906941284</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.3725603991662041</v>
+        <v>-0.37253849513381</v>
       </c>
     </row>
     <row r="123">
@@ -3240,16 +3240,16 @@
         <v>-0.2327002848835207</v>
       </c>
       <c r="D123" t="n">
-        <v>146.5605817737445</v>
+        <v>146.5700385220727</v>
       </c>
       <c r="E123" t="n">
-        <v>0.6381898543299087</v>
+        <v>0.6499331573729989</v>
       </c>
       <c r="F123" t="n">
-        <v>146.0166351235369</v>
+        <v>146.0167406666192</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.3870445309988497</v>
+        <v>-0.3871154350426025</v>
       </c>
     </row>
     <row r="124">
@@ -3263,16 +3263,16 @@
         <v>-3.257020798318578</v>
       </c>
       <c r="D124" t="n">
-        <v>145.4072285688906</v>
+        <v>145.4053676152743</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.7869463882412902</v>
+        <v>-0.7946173164326495</v>
       </c>
       <c r="F124" t="n">
-        <v>145.4605867422824</v>
+        <v>145.4605920191254</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.3808116662763013</v>
+        <v>-0.3808800586527212</v>
       </c>
     </row>
     <row r="125">
@@ -3286,16 +3286,16 @@
         <v>-2.308659444374712</v>
       </c>
       <c r="D125" t="n">
-        <v>145.033734228584</v>
+        <v>145.0327835415146</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.2568609167388445</v>
+        <v>-0.2562381842364374</v>
       </c>
       <c r="F125" t="n">
-        <v>144.9522577703783</v>
+        <v>144.9522443787708</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.3494616536950588</v>
+        <v>-0.3494744750438485</v>
       </c>
     </row>
     <row r="126">
@@ -3309,16 +3309,16 @@
         <v>-2.244541959638084</v>
       </c>
       <c r="D126" t="n">
-        <v>145.3491156847489</v>
+        <v>145.3464628707462</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2174538619186421</v>
+        <v>0.2162816720274776</v>
       </c>
       <c r="F126" t="n">
-        <v>144.5261740362779</v>
+        <v>144.5262972736429</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.293947635348573</v>
+        <v>-0.2938534045840271</v>
       </c>
     </row>
     <row r="127">
@@ -3332,16 +3332,16 @@
         <v>-1.579516830710119</v>
       </c>
       <c r="D127" t="n">
-        <v>144.5358084810877</v>
+        <v>144.5394119821883</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.5595542840626422</v>
+        <v>-0.5552600817507169</v>
       </c>
       <c r="F127" t="n">
-        <v>144.2120986900499</v>
+        <v>144.2124846714865</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.2173138175989635</v>
+        <v>-0.2171318355732836</v>
       </c>
     </row>
     <row r="128">
@@ -3355,16 +3355,16 @@
         <v>-3.521629604031801</v>
       </c>
       <c r="D128" t="n">
-        <v>144.0019048757248</v>
+        <v>143.9952489722772</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.3693919250694506</v>
+        <v>-0.3764807137711159</v>
       </c>
       <c r="F128" t="n">
-        <v>144.0351616158424</v>
+        <v>144.0359566587496</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.1226922538502464</v>
+        <v>-0.1224082735548535</v>
       </c>
     </row>
     <row r="129">
@@ -3378,16 +3378,16 @@
         <v>-5.603061815356199</v>
       </c>
       <c r="D129" t="n">
-        <v>143.7269581956133</v>
+        <v>143.7315308773142</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.1909326688064965</v>
+        <v>-0.1831436084490576</v>
       </c>
       <c r="F129" t="n">
-        <v>144.0128212932694</v>
+        <v>144.0141416526218</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.01551032561938825</v>
+        <v>-0.01514552798744262</v>
       </c>
     </row>
     <row r="130">
@@ -3401,16 +3401,16 @@
         <v>-3.595875372522471</v>
       </c>
       <c r="D130" t="n">
-        <v>143.4381952271876</v>
+        <v>143.4402784489625</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.2009107908849899</v>
+        <v>-0.2026364198404735</v>
       </c>
       <c r="F130" t="n">
-        <v>144.1525790995705</v>
+        <v>144.1544866702519</v>
       </c>
       <c r="G130" t="n">
-        <v>0.09704539154647307</v>
+        <v>0.09745224741095626</v>
       </c>
     </row>
     <row r="131">
@@ -3424,16 +3424,16 @@
         <v>-3.594336985895922</v>
       </c>
       <c r="D131" t="n">
-        <v>143.9538562955942</v>
+        <v>143.9510808343157</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3595005274500664</v>
+        <v>0.3561080547783035</v>
       </c>
       <c r="F131" t="n">
-        <v>144.4512445191311</v>
+        <v>144.4538328710644</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2071870107535716</v>
+        <v>0.2076565271930946</v>
       </c>
     </row>
     <row r="132">
@@ -3447,16 +3447,16 @@
         <v>-3.307094302888586</v>
       </c>
       <c r="D132" t="n">
-        <v>144.782913266767</v>
+        <v>144.7871024251988</v>
       </c>
       <c r="E132" t="n">
-        <v>0.5759185564785838</v>
+        <v>0.5807678456025656</v>
       </c>
       <c r="F132" t="n">
-        <v>144.8919301907489</v>
+        <v>144.8950835484986</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3050757181669184</v>
+        <v>0.3054613842112559</v>
       </c>
     </row>
     <row r="133">
@@ -3470,16 +3470,16 @@
         <v>-1.501604882296022</v>
       </c>
       <c r="D133" t="n">
-        <v>144.8303443045974</v>
+        <v>144.8289306074739</v>
       </c>
       <c r="E133" t="n">
-        <v>0.03276010736361457</v>
+        <v>0.02888943944215328</v>
       </c>
       <c r="F133" t="n">
-        <v>145.4493659182457</v>
+        <v>145.4526803436079</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3847251719008256</v>
+        <v>0.3848279606551728</v>
       </c>
     </row>
     <row r="134">
@@ -3493,16 +3493,16 @@
         <v>-2.878536664210387</v>
       </c>
       <c r="D134" t="n">
-        <v>144.3149798691156</v>
+        <v>144.3154675558232</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.3558400954967453</v>
+        <v>-0.3545307208283788</v>
       </c>
       <c r="F134" t="n">
-        <v>146.0887694638583</v>
+        <v>146.0916188499597</v>
       </c>
       <c r="G134" t="n">
-        <v>0.4396055916613903</v>
+        <v>0.4392758557920473</v>
       </c>
     </row>
     <row r="135">
@@ -3516,16 +3516,16 @@
         <v>0.1068639368744471</v>
       </c>
       <c r="D135" t="n">
-        <v>148.1550156324322</v>
+        <v>148.1540180452249</v>
       </c>
       <c r="E135" t="n">
-        <v>2.660871218496695</v>
+        <v>2.659833041054213</v>
       </c>
       <c r="F135" t="n">
-        <v>146.7650227766711</v>
+        <v>146.7666972268364</v>
       </c>
       <c r="G135" t="n">
-        <v>0.462905749219928</v>
+        <v>0.4620924747024588</v>
       </c>
     </row>
     <row r="136">
@@ -3539,16 +3539,16 @@
         <v>3.370179948355684</v>
       </c>
       <c r="D136" t="n">
-        <v>147.4682751717338</v>
+        <v>147.4687850722651</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.4635283238754226</v>
+        <v>-0.4625139311109479</v>
       </c>
       <c r="F136" t="n">
-        <v>147.4295927262034</v>
+        <v>147.4294555618643</v>
       </c>
       <c r="G136" t="n">
-        <v>0.4528122143540685</v>
+        <v>0.4515726984055703</v>
       </c>
     </row>
     <row r="137">
@@ -3562,16 +3562,16 @@
         <v>3.376076942076395</v>
       </c>
       <c r="D137" t="n">
-        <v>149.8274823011002</v>
+        <v>149.8310480448698</v>
       </c>
       <c r="E137" t="n">
-        <v>1.599806552710419</v>
+        <v>1.601873217743787</v>
       </c>
       <c r="F137" t="n">
-        <v>148.036978980685</v>
+        <v>148.0346174780666</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4119839465402322</v>
+        <v>0.4104755823020554</v>
       </c>
     </row>
     <row r="138">
@@ -3585,16 +3585,16 @@
         <v>2.851866123943239</v>
       </c>
       <c r="D138" t="n">
-        <v>149.8237445882036</v>
+        <v>149.823057256547</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.002494677771537113</v>
+        <v>-0.005333199244788034</v>
       </c>
       <c r="F138" t="n">
-        <v>148.5420680975833</v>
+        <v>148.5373232373677</v>
       </c>
       <c r="G138" t="n">
-        <v>0.3411911809982229</v>
+        <v>0.3395866236324991</v>
       </c>
     </row>
     <row r="139">
@@ -3608,16 +3608,16 @@
         <v>5.938658451965011</v>
       </c>
       <c r="D139" t="n">
-        <v>150.4183634074499</v>
+        <v>150.41548499537</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3968788931825458</v>
+        <v>0.3954182685035761</v>
       </c>
       <c r="F139" t="n">
-        <v>148.9083163406445</v>
+        <v>148.9013335707005</v>
       </c>
       <c r="G139" t="n">
-        <v>0.2465619657460678</v>
+        <v>0.2450632106458102</v>
       </c>
     </row>
     <row r="140">
@@ -3631,16 +3631,16 @@
         <v>4.416076435379892</v>
       </c>
       <c r="D140" t="n">
-        <v>150.625556024051</v>
+        <v>150.6199706186292</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1377442300976668</v>
+        <v>0.1359471887255808</v>
       </c>
       <c r="F140" t="n">
-        <v>149.1114670184999</v>
+        <v>149.102706268922</v>
       </c>
       <c r="G140" t="n">
-        <v>0.136426683779419</v>
+        <v>0.1352390159258476</v>
       </c>
     </row>
     <row r="141">
@@ -3654,16 +3654,16 @@
         <v>4.539273716820986</v>
       </c>
       <c r="D141" t="n">
-        <v>150.2783321405601</v>
+        <v>150.2826270245394</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.2305212293692449</v>
+        <v>-0.2239700304708947</v>
       </c>
       <c r="F141" t="n">
-        <v>149.142867490271</v>
+        <v>149.133048725841</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02105838833121254</v>
+        <v>0.02035003768760646</v>
       </c>
     </row>
     <row r="142">
@@ -3677,16 +3677,16 @@
         <v>2.937925301082501</v>
       </c>
       <c r="D142" t="n">
-        <v>148.9796307916533</v>
+        <v>148.9809213131295</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.8641973399678733</v>
+        <v>-0.8661717839130887</v>
       </c>
       <c r="F142" t="n">
-        <v>149.0038418312049</v>
+        <v>148.9937671585945</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.09321643160387794</v>
+        <v>-0.09339416610639262</v>
       </c>
     </row>
     <row r="143">
@@ -3700,16 +3700,16 @@
         <v>2.578649650709437</v>
       </c>
       <c r="D143" t="n">
-        <v>149.3637856082429</v>
+        <v>149.3621534196348</v>
       </c>
       <c r="E143" t="n">
-        <v>0.2578572752182566</v>
+        <v>0.2558932399834077</v>
       </c>
       <c r="F143" t="n">
-        <v>148.7070999390566</v>
+        <v>148.697567928567</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.1991504973974969</v>
+        <v>-0.1987997455707102</v>
       </c>
     </row>
     <row r="144">
@@ -3723,16 +3723,16 @@
         <v>3.760700497475767</v>
       </c>
       <c r="D144" t="n">
-        <v>148.5206574831106</v>
+        <v>148.5204271339802</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.5644796171299902</v>
+        <v>-0.5635472349476203</v>
       </c>
       <c r="F144" t="n">
-        <v>148.2803624691182</v>
+        <v>148.2720143787373</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.2869650945471562</v>
+        <v>-0.2861872966436749</v>
       </c>
     </row>
     <row r="145">
@@ -3746,16 +3746,16 @@
         <v>1.072503954214284</v>
       </c>
       <c r="D145" t="n">
-        <v>146.9231202448977</v>
+        <v>146.9249827826692</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.07563302323419</v>
+        <v>-1.074225533886818</v>
       </c>
       <c r="F145" t="n">
-        <v>147.7593137106077</v>
+        <v>147.7525880753755</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.3513943113127738</v>
+        <v>-0.3503198533709906</v>
       </c>
     </row>
     <row r="146">
@@ -3769,16 +3769,16 @@
         <v>0.5584115340199816</v>
       </c>
       <c r="D146" t="n">
-        <v>147.887593170922</v>
+        <v>147.8882607099801</v>
       </c>
       <c r="E146" t="n">
-        <v>0.6564473477126143</v>
+        <v>0.6556256867055623</v>
       </c>
       <c r="F146" t="n">
-        <v>147.1842457909818</v>
+        <v>147.179324945783</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.3891923325741686</v>
+        <v>-0.3879885537436962</v>
       </c>
     </row>
     <row r="147">
@@ -3792,16 +3792,16 @@
         <v>1.209756198096002</v>
       </c>
       <c r="D147" t="n">
-        <v>146.9283020597886</v>
+        <v>146.9261531216244</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.6486623323598906</v>
+        <v>-0.6505638674340304</v>
       </c>
       <c r="F147" t="n">
-        <v>146.5976043569459</v>
+        <v>146.5944238734953</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.3985762408763662</v>
+        <v>-0.3974070899585627</v>
       </c>
     </row>
     <row r="148">
@@ -3815,16 +3815,16 @@
         <v>0.4543777110976919</v>
       </c>
       <c r="D148" t="n">
-        <v>145.941668237428</v>
+        <v>145.9431496365663</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.6715069925460142</v>
+        <v>-0.6690459555177881</v>
       </c>
       <c r="F148" t="n">
-        <v>146.0431246961607</v>
+        <v>146.0414106038301</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.3782324160189887</v>
+        <v>-0.3772403172322782</v>
       </c>
     </row>
     <row r="149">
@@ -3838,16 +3838,16 @@
         <v>-2.6884693380333</v>
       </c>
       <c r="D149" t="n">
-        <v>144.9015523863129</v>
+        <v>144.9036786139955</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.7126928612485131</v>
+        <v>-0.7122437916128632</v>
       </c>
       <c r="F149" t="n">
-        <v>145.5581795378368</v>
+        <v>145.5574952808229</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.3320561370710067</v>
+        <v>-0.3313548677778186</v>
       </c>
     </row>
     <row r="150">
@@ -3861,16 +3861,16 @@
         <v>-3.181133606712237</v>
       </c>
       <c r="D150" t="n">
-        <v>144.3862971154904</v>
+        <v>144.3848072476054</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.3555898900577432</v>
+        <v>-0.3580801890974357</v>
       </c>
       <c r="F150" t="n">
-        <v>145.1703212006199</v>
+        <v>145.1701661012411</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.2664627563002142</v>
+        <v>-0.2661004703567613</v>
       </c>
     </row>
     <row r="151">
@@ -3884,16 +3884,16 @@
         <v>-5.692551456485901</v>
       </c>
       <c r="D151" t="n">
-        <v>144.4045978214091</v>
+        <v>144.4039614616447</v>
       </c>
       <c r="E151" t="n">
-        <v>0.01267482183857283</v>
+        <v>0.01326608692731668</v>
       </c>
       <c r="F151" t="n">
-        <v>144.8999716887359</v>
+        <v>144.8999515350107</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.1862291890299019</v>
+        <v>-0.1861364311190243</v>
       </c>
     </row>
     <row r="152">
@@ -3907,16 +3907,16 @@
         <v>-5.343413509496074</v>
       </c>
       <c r="D152" t="n">
-        <v>144.5902486406117</v>
+        <v>144.5872581686741</v>
       </c>
       <c r="E152" t="n">
-        <v>0.1285629557531252</v>
+        <v>0.1269332954401392</v>
       </c>
       <c r="F152" t="n">
-        <v>144.7578735335625</v>
+        <v>144.7576425693146</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.09806637883868063</v>
+        <v>-0.09821187943028065</v>
       </c>
     </row>
     <row r="153">
@@ -3930,16 +3930,16 @@
         <v>-1.905549636865743</v>
       </c>
       <c r="D153" t="n">
-        <v>145.51215513351</v>
+        <v>145.514797168503</v>
       </c>
       <c r="E153" t="n">
-        <v>0.6375993551195052</v>
+        <v>0.6415081187491865</v>
       </c>
       <c r="F153" t="n">
-        <v>144.7480690113329</v>
+        <v>144.7474274637941</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.006773049361839867</v>
+        <v>-0.007056695134849633</v>
       </c>
     </row>
     <row r="154">
@@ -3953,16 +3953,16 @@
         <v>-2.655966930753095</v>
       </c>
       <c r="D154" t="n">
-        <v>145.1348282111025</v>
+        <v>145.1351766480802</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.2593095553160509</v>
+        <v>-0.2608810428970685</v>
       </c>
       <c r="F154" t="n">
-        <v>144.8700984629687</v>
+        <v>144.8690413861981</v>
       </c>
       <c r="G154" t="n">
-        <v>0.084304718169534</v>
+        <v>0.08401801989499802</v>
       </c>
     </row>
     <row r="155">
@@ -3976,16 +3976,16 @@
         <v>-4.018482537497235</v>
       </c>
       <c r="D155" t="n">
-        <v>145.1063094326301</v>
+        <v>145.1106348110024</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.0196498516750836</v>
+        <v>-0.01690964082220603</v>
       </c>
       <c r="F155" t="n">
-        <v>145.1157753737068</v>
+        <v>145.1144473538895</v>
       </c>
       <c r="G155" t="n">
-        <v>0.169584278153053</v>
+        <v>0.1693984893826439</v>
       </c>
     </row>
     <row r="156">
@@ -3999,16 +3999,16 @@
         <v>-0.8464209501952382</v>
       </c>
       <c r="D156" t="n">
-        <v>145.6975240645707</v>
+        <v>145.6940046400068</v>
       </c>
       <c r="E156" t="n">
-        <v>0.4074355100424469</v>
+        <v>0.4020172813413723</v>
       </c>
       <c r="F156" t="n">
-        <v>145.4714835346595</v>
+        <v>145.4699917152826</v>
       </c>
       <c r="G156" t="n">
-        <v>0.2451202565928412</v>
+        <v>0.2450096236979391</v>
       </c>
     </row>
     <row r="157">
@@ -4022,16 +4022,16 @@
         <v>0.4565427312700479</v>
       </c>
       <c r="D157" t="n">
-        <v>147.0802778465696</v>
+        <v>147.0794718927929</v>
       </c>
       <c r="E157" t="n">
-        <v>0.9490578449267986</v>
+        <v>0.9509432156865216</v>
       </c>
       <c r="F157" t="n">
-        <v>145.9241850849348</v>
+        <v>145.9226977675214</v>
       </c>
       <c r="G157" t="n">
-        <v>0.311196077248681</v>
+        <v>0.3112023633883467</v>
       </c>
     </row>
     <row r="158">
@@ -4045,16 +4045,16 @@
         <v>1.399820970331206</v>
       </c>
       <c r="D158" t="n">
-        <v>146.8861511920682</v>
+        <v>146.8844380880566</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.1319868695814677</v>
+        <v>-0.1326043683910143</v>
       </c>
       <c r="F158" t="n">
-        <v>146.4574413222611</v>
+        <v>146.4561365569342</v>
       </c>
       <c r="G158" t="n">
-        <v>0.3654337606997302</v>
+        <v>0.3655625872971626</v>
       </c>
     </row>
     <row r="159">
@@ -4068,16 +4068,16 @@
         <v>-1.544966268011734</v>
       </c>
       <c r="D159" t="n">
-        <v>146.9167302711149</v>
+        <v>146.9154392385229</v>
       </c>
       <c r="E159" t="n">
-        <v>0.02081821791812821</v>
+        <v>0.02110581002985334</v>
       </c>
       <c r="F159" t="n">
-        <v>147.0516663753218</v>
+        <v>147.050654141331</v>
       </c>
       <c r="G159" t="n">
-        <v>0.4057322370893734</v>
+        <v>0.4059355916204765</v>
       </c>
     </row>
     <row r="160">
@@ -4091,16 +4091,16 @@
         <v>1.687720608810153</v>
       </c>
       <c r="D160" t="n">
-        <v>147.7874717235352</v>
+        <v>147.7904758601711</v>
       </c>
       <c r="E160" t="n">
-        <v>0.5926768522641623</v>
+        <v>0.5956056260550957</v>
       </c>
       <c r="F160" t="n">
-        <v>147.6868040657892</v>
+        <v>147.6861199011726</v>
       </c>
       <c r="G160" t="n">
-        <v>0.4319146502198112</v>
+        <v>0.4321407229041396</v>
       </c>
     </row>
     <row r="161">
@@ -4114,16 +4114,16 @@
         <v>-0.8511085302119454</v>
       </c>
       <c r="D161" t="n">
-        <v>147.8052142763988</v>
+        <v>147.8102831875489</v>
       </c>
       <c r="E161" t="n">
-        <v>0.01200545124471208</v>
+        <v>0.01340230299857748</v>
       </c>
       <c r="F161" t="n">
-        <v>148.341168620822</v>
+        <v>148.3407725910139</v>
       </c>
       <c r="G161" t="n">
-        <v>0.4430758449761818</v>
+        <v>0.4432729970015536</v>
       </c>
     </row>
     <row r="162">
@@ -4137,16 +4137,16 @@
         <v>2.981771021694684</v>
       </c>
       <c r="D162" t="n">
-        <v>148.5388521615936</v>
+        <v>148.5412264044742</v>
       </c>
       <c r="E162" t="n">
-        <v>0.4963545357898447</v>
+        <v>0.4945144553967662</v>
       </c>
       <c r="F162" t="n">
-        <v>148.9873077539492</v>
+        <v>148.9871157221859</v>
       </c>
       <c r="G162" t="n">
-        <v>0.4355764075034019</v>
+        <v>0.4357150902496887</v>
       </c>
     </row>
     <row r="163">
@@ -4160,16 +4160,16 @@
         <v>4.798574571620946</v>
       </c>
       <c r="D163" t="n">
-        <v>150.3065796819617</v>
+        <v>150.2991365279626</v>
       </c>
       <c r="E163" t="n">
-        <v>1.190077541763301</v>
+        <v>1.18344931305574</v>
       </c>
       <c r="F163" t="n">
-        <v>149.5946537808621</v>
+        <v>149.594560433542</v>
       </c>
       <c r="G163" t="n">
-        <v>0.4076495079137654</v>
+        <v>0.4077162702369463</v>
       </c>
     </row>
     <row r="164">
@@ -4183,16 +4183,16 @@
         <v>4.574479077392752</v>
       </c>
       <c r="D164" t="n">
-        <v>150.4181143903687</v>
+        <v>150.4229645186726</v>
       </c>
       <c r="E164" t="n">
-        <v>0.07420480769575466</v>
+        <v>0.08238769268444912</v>
       </c>
       <c r="F164" t="n">
-        <v>150.1294112701921</v>
+        <v>150.1293106078147</v>
       </c>
       <c r="G164" t="n">
-        <v>0.3574709896473127</v>
+        <v>0.3574663227880137</v>
       </c>
     </row>
     <row r="165">
@@ -4206,16 +4206,16 @@
         <v>3.884652851381773</v>
       </c>
       <c r="D165" t="n">
-        <v>150.3609965567473</v>
+        <v>150.358653535333</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.03797270950575138</v>
+        <v>-0.04275343432125212</v>
       </c>
       <c r="F165" t="n">
-        <v>150.5559297275577</v>
+        <v>150.5557261476177</v>
       </c>
       <c r="G165" t="n">
-        <v>0.2841005328383162</v>
+        <v>0.2840321707177518</v>
       </c>
     </row>
     <row r="166">
@@ -4229,16 +4229,16 @@
         <v>3.08350959869108</v>
       </c>
       <c r="D166" t="n">
-        <v>151.2726087965529</v>
+        <v>151.2701016896966</v>
       </c>
       <c r="E166" t="n">
-        <v>0.6062823875083945</v>
+        <v>0.6061827057725289</v>
       </c>
       <c r="F166" t="n">
-        <v>150.8384787894923</v>
+        <v>150.8380832449387</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1876704972337828</v>
+        <v>0.187543246973032</v>
       </c>
     </row>
     <row r="167">
@@ -4252,16 +4252,16 @@
         <v>5.844742596065089</v>
       </c>
       <c r="D167" t="n">
-        <v>151.5552386450351</v>
+        <v>151.5506024147731</v>
       </c>
       <c r="E167" t="n">
-        <v>0.1868347817431504</v>
+        <v>0.1854303804540436</v>
       </c>
       <c r="F167" t="n">
-        <v>150.9496366349137</v>
+        <v>150.9490529538892</v>
       </c>
       <c r="G167" t="n">
-        <v>0.07369329518134293</v>
+        <v>0.07356876099406939</v>
       </c>
     </row>
     <row r="168">
@@ -4275,16 +4275,16 @@
         <v>4.821169570894781</v>
       </c>
       <c r="D168" t="n">
-        <v>152.6704257450405</v>
+        <v>152.6717032270308</v>
       </c>
       <c r="E168" t="n">
-        <v>0.7358288040555605</v>
+        <v>0.7397534515827697</v>
       </c>
       <c r="F168" t="n">
-        <v>150.8665881491821</v>
+        <v>150.8658500937239</v>
       </c>
       <c r="G168" t="n">
-        <v>-0.05501734723116769</v>
+        <v>-0.05511982919880198</v>
       </c>
     </row>
     <row r="169">
@@ -4298,16 +4298,16 @@
         <v>2.940764064859309</v>
       </c>
       <c r="D169" t="n">
-        <v>152.3083212482753</v>
+        <v>152.3116799965811</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.2371805115483516</v>
+        <v>-0.2358152970326821</v>
       </c>
       <c r="F169" t="n">
-        <v>150.5787176926189</v>
+        <v>150.5778746952176</v>
       </c>
       <c r="G169" t="n">
-        <v>-0.1908112724591682</v>
+        <v>-0.1908817657059747</v>
       </c>
     </row>
     <row r="170">
@@ -4321,16 +4321,16 @@
         <v>4.470565929197079</v>
       </c>
       <c r="D170" t="n">
-        <v>150.8164785477397</v>
+        <v>150.8186657918889</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.9794886374617562</v>
+        <v>-0.9802361872219905</v>
       </c>
       <c r="F170" t="n">
-        <v>150.0918961442838</v>
+        <v>150.0909607527091</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.3233003679370654</v>
+        <v>-0.3233635376339663</v>
       </c>
     </row>
     <row r="171">
@@ -4344,16 +4344,16 @@
         <v>5.039042655950277</v>
       </c>
       <c r="D171" t="n">
-        <v>152.3130032189767</v>
+        <v>152.3148001763975</v>
       </c>
       <c r="E171" t="n">
-        <v>0.9922819347378153</v>
+        <v>0.9920087653958687</v>
       </c>
       <c r="F171" t="n">
-        <v>149.4278035300679</v>
+        <v>149.4267595721464</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.4424573419856692</v>
+        <v>-0.4425324331537084</v>
       </c>
     </row>
     <row r="172">
@@ -4367,16 +4367,16 @@
         <v>2.120521982870471</v>
       </c>
       <c r="D172" t="n">
-        <v>151.6440897331238</v>
+        <v>151.6401055315875</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.4391703083230669</v>
+        <v>-0.4429606604404945</v>
       </c>
       <c r="F172" t="n">
-        <v>148.6228833671057</v>
+        <v>148.6216799162118</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.538668269188769</v>
+        <v>-0.5387787691038648</v>
       </c>
     </row>
     <row r="173">
@@ -4390,16 +4390,16 @@
         <v>-0.2775985306436191</v>
       </c>
       <c r="D173" t="n">
-        <v>146.8445772433043</v>
+        <v>146.8472154238205</v>
       </c>
       <c r="E173" t="n">
-        <v>-3.164984865724785</v>
+        <v>-3.160700852169107</v>
       </c>
       <c r="F173" t="n">
-        <v>147.7217901328169</v>
+        <v>147.7203513964143</v>
       </c>
       <c r="G173" t="n">
-        <v>-0.6062950831488556</v>
+        <v>-0.6064583042699856</v>
       </c>
     </row>
     <row r="174">
@@ -4413,16 +4413,16 @@
         <v>-5.239360122452529</v>
       </c>
       <c r="D174" t="n">
-        <v>144.5435460143961</v>
+        <v>144.5453136894268</v>
       </c>
       <c r="E174" t="n">
-        <v>-1.566984135270866</v>
+        <v>-1.567548780377037</v>
       </c>
       <c r="F174" t="n">
-        <v>146.7774119202097</v>
+        <v>146.7756587667716</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.6392951315835171</v>
+        <v>-0.6395142041787039</v>
       </c>
     </row>
     <row r="175">
@@ -4436,16 +4436,16 @@
         <v>-6.153867204717778</v>
       </c>
       <c r="D175" t="n">
-        <v>143.2777304836204</v>
+        <v>143.2733246281045</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.8757329992787333</v>
+        <v>-0.8799932898933216</v>
       </c>
       <c r="F175" t="n">
-        <v>145.8453454251972</v>
+        <v>145.8431726948627</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.6350203909571972</v>
+        <v>-0.6353138386458013</v>
       </c>
     </row>
     <row r="176">
@@ -4459,16 +4459,16 @@
         <v>-2.889122354246665</v>
       </c>
       <c r="D176" t="n">
-        <v>143.4784046294814</v>
+        <v>143.4767119869885</v>
       </c>
       <c r="E176" t="n">
-        <v>0.140059550904148</v>
+        <v>0.1419575900900361</v>
       </c>
       <c r="F176" t="n">
-        <v>144.9773466905263</v>
+        <v>144.9746519677514</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.5951501106465362</v>
+        <v>-0.5955168905495967</v>
       </c>
     </row>
     <row r="177">
@@ -4482,16 +4482,16 @@
         <v>-1.667868428317143</v>
       </c>
       <c r="D177" t="n">
-        <v>146.6859767064804</v>
+        <v>146.6812232942065</v>
       </c>
       <c r="E177" t="n">
-        <v>2.235578298547591</v>
+        <v>2.233471385592245</v>
       </c>
       <c r="F177" t="n">
-        <v>144.2205317746586</v>
+        <v>144.2173441064462</v>
       </c>
       <c r="G177" t="n">
-        <v>-0.5220228767761848</v>
+        <v>-0.5223726017108743</v>
       </c>
     </row>
     <row r="178">
@@ -4505,16 +4505,16 @@
         <v>-5.902174324819032</v>
       </c>
       <c r="D178" t="n">
-        <v>143.0665818653548</v>
+        <v>143.0730279201513</v>
       </c>
       <c r="E178" t="n">
-        <v>-2.467444347708891</v>
+        <v>-2.459889066249454</v>
       </c>
       <c r="F178" t="n">
-        <v>143.6088986230146</v>
+        <v>143.6053253610546</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.4240957539940582</v>
+        <v>-0.4243724977627261</v>
       </c>
     </row>
     <row r="179">
@@ -4528,16 +4528,16 @@
         <v>-4.379711543203713</v>
       </c>
       <c r="D179" t="n">
-        <v>143.4813873923554</v>
+        <v>143.4804306631584</v>
       </c>
       <c r="E179" t="n">
-        <v>0.2899387974412138</v>
+        <v>0.2847516047779886</v>
       </c>
       <c r="F179" t="n">
-        <v>143.1592961867234</v>
+        <v>143.1554931970786</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.3130742179643375</v>
+        <v>-0.3132419796028074</v>
       </c>
     </row>
     <row r="180">
@@ -4551,16 +4551,16 @@
         <v>-7.459968886131019</v>
       </c>
       <c r="D180" t="n">
-        <v>141.6963954959773</v>
+        <v>141.6918961144313</v>
       </c>
       <c r="E180" t="n">
-        <v>-1.244058151944849</v>
+        <v>-1.246535531333881</v>
       </c>
       <c r="F180" t="n">
-        <v>142.8743084620578</v>
+        <v>142.8704359895568</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.1990703588636955</v>
+        <v>-0.199124183889543</v>
       </c>
     </row>
     <row r="181">
@@ -4574,16 +4574,16 @@
         <v>-7.175041607523447</v>
       </c>
       <c r="D181" t="n">
-        <v>141.9484547852458</v>
+        <v>141.953910896018</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1778868745293538</v>
+        <v>0.1849186783237533</v>
       </c>
       <c r="F181" t="n">
-        <v>142.7411796252686</v>
+        <v>142.7373711468162</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.09317898943635994</v>
+        <v>-0.09313672336686007</v>
       </c>
     </row>
     <row r="182">
@@ -4597,16 +4597,16 @@
         <v>-5.747947522315089</v>
       </c>
       <c r="D182" t="n">
-        <v>141.3468168733616</v>
+        <v>141.3470074226524</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.4238425228329734</v>
+        <v>-0.4275355779454926</v>
       </c>
       <c r="F182" t="n">
-        <v>142.732433256577</v>
+        <v>142.7287992007319</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.006127431981861609</v>
+        <v>-0.006005397195851803</v>
       </c>
     </row>
     <row r="183">
@@ -4620,16 +4620,16 @@
         <v>-4.718516211817859</v>
       </c>
       <c r="D183" t="n">
-        <v>143.7521766040946</v>
+        <v>143.7598655034413</v>
       </c>
       <c r="E183" t="n">
-        <v>1.701743119470489</v>
+        <v>1.707045748463565</v>
       </c>
       <c r="F183" t="n">
-        <v>142.8107456407321</v>
+        <v>142.8073655306258</v>
       </c>
       <c r="G183" t="n">
-        <v>0.05486656562092573</v>
+        <v>0.0550458844562618</v>
       </c>
     </row>
     <row r="184">
@@ -4643,16 +4643,16 @@
         <v>-6.989767700656724</v>
       </c>
       <c r="D184" t="n">
-        <v>142.3342294725312</v>
+        <v>142.3263500239227</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.9863830691541398</v>
+        <v>-0.9971597250029052</v>
       </c>
       <c r="F184" t="n">
-        <v>142.9337991042856</v>
+        <v>142.9307226517682</v>
       </c>
       <c r="G184" t="n">
-        <v>0.08616540933352734</v>
+        <v>0.08638008318693213</v>
       </c>
     </row>
     <row r="185">
@@ -4666,16 +4666,16 @@
         <v>-1.061427104899348</v>
       </c>
       <c r="D185" t="n">
-        <v>142.5328199775203</v>
+        <v>142.5285168273246</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1395240665053477</v>
+        <v>0.1420445359330946</v>
       </c>
       <c r="F185" t="n">
-        <v>143.0556043114069</v>
+        <v>143.0528241028266</v>
       </c>
       <c r="G185" t="n">
-        <v>0.08521791758462349</v>
+        <v>0.08542701582492374</v>
       </c>
     </row>
     <row r="186">
@@ -4689,16 +4689,16 @@
         <v>2.863383723705004</v>
       </c>
       <c r="D186" t="n">
-        <v>145.0222170518212</v>
+        <v>145.0210426398141</v>
       </c>
       <c r="E186" t="n">
-        <v>1.746543059130867</v>
+        <v>1.748790956345414</v>
       </c>
       <c r="F186" t="n">
-        <v>143.1351279409223</v>
+        <v>143.1326325650725</v>
       </c>
       <c r="G186" t="n">
-        <v>0.05558931430769132</v>
+        <v>0.05578950485349843</v>
       </c>
     </row>
     <row r="187">
@@ -4712,16 +4712,16 @@
         <v>-0.1765360760572654</v>
       </c>
       <c r="D187" t="n">
-        <v>143.9990787967812</v>
+        <v>144.0045563590138</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.7055044915458608</v>
+        <v>-0.7009233020927597</v>
       </c>
       <c r="F187" t="n">
-        <v>143.1383030930447</v>
+        <v>143.1360822535978</v>
       </c>
       <c r="G187" t="n">
-        <v>0.002218289925104422</v>
+        <v>0.002410134197572411</v>
       </c>
     </row>
     <row r="188">
@@ -4735,16 +4735,16 @@
         <v>0.5573345897494031</v>
       </c>
       <c r="D188" t="n">
-        <v>145.8239841118597</v>
+        <v>145.8222101424362</v>
       </c>
       <c r="E188" t="n">
-        <v>1.267303464943592</v>
+        <v>1.262219633447481</v>
       </c>
       <c r="F188" t="n">
-        <v>143.0389065391494</v>
+        <v>143.0369573152659</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.06944091954945719</v>
+        <v>-0.06925223659277613</v>
       </c>
     </row>
     <row r="189">
@@ -4758,16 +4758,16 @@
         <v>-3.739985315411354</v>
       </c>
       <c r="D189" t="n">
-        <v>144.8882724442373</v>
+        <v>144.8850603908832</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.6416719947142768</v>
+        <v>-0.6426659907551646</v>
       </c>
       <c r="F189" t="n">
-        <v>142.8211067832097</v>
+        <v>142.8194829773504</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.1522660940365239</v>
+        <v>-0.1520406627751769</v>
       </c>
     </row>
     <row r="190">
@@ -4781,16 +4781,16 @@
         <v>-2.083175823958838</v>
       </c>
       <c r="D190" t="n">
-        <v>140.4451632754095</v>
+        <v>140.4501492982151</v>
       </c>
       <c r="E190" t="n">
-        <v>-3.066576123707909</v>
+        <v>-3.060985777762881</v>
       </c>
       <c r="F190" t="n">
-        <v>142.4799816919654</v>
+        <v>142.4787960331683</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.2388478138333761</v>
+        <v>-0.2385437456289718</v>
       </c>
     </row>
     <row r="191">
@@ -4804,16 +4804,16 @@
         <v>-0.8428393701106929</v>
       </c>
       <c r="D191" t="n">
-        <v>143.7918715601473</v>
+        <v>143.7865372685019</v>
       </c>
       <c r="E191" t="n">
-        <v>2.382928829079711</v>
+        <v>2.375496207699079</v>
       </c>
       <c r="F191" t="n">
-        <v>142.0210363145759</v>
+        <v>142.020414892684</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.3221121816127992</v>
+        <v>-0.3217188474680555</v>
       </c>
     </row>
     <row r="192">
@@ -4827,16 +4827,16 @@
         <v>-2.006209090279898</v>
       </c>
       <c r="D192" t="n">
-        <v>140.8671749687223</v>
+        <v>140.8650002198603</v>
       </c>
       <c r="E192" t="n">
-        <v>-2.03397908358236</v>
+        <v>-2.031857157242789</v>
       </c>
       <c r="F192" t="n">
-        <v>141.4602566003798</v>
+        <v>141.4602476222375</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.3948567963931282</v>
+        <v>-0.3944272877035249</v>
       </c>
     </row>
     <row r="193">
@@ -4850,16 +4850,16 @@
         <v>-0.3570316857980038</v>
       </c>
       <c r="D193" t="n">
-        <v>139.9818226781998</v>
+        <v>139.9893317187354</v>
       </c>
       <c r="E193" t="n">
-        <v>-0.6285014878157691</v>
+        <v>-0.6216366732390455</v>
       </c>
       <c r="F193" t="n">
-        <v>140.8261921537895</v>
+        <v>140.8267828889595</v>
       </c>
       <c r="G193" t="n">
-        <v>-0.4482279771211406</v>
+        <v>-0.4478040608055345</v>
       </c>
     </row>
     <row r="194">
@@ -4873,16 +4873,16 @@
         <v>-0.4795390207207983</v>
       </c>
       <c r="D194" t="n">
-        <v>141.0272280122697</v>
+        <v>141.0276687938854</v>
       </c>
       <c r="E194" t="n">
-        <v>0.746815060747652</v>
+        <v>0.7417258603935384</v>
       </c>
       <c r="F194" t="n">
-        <v>140.1484809583501</v>
+        <v>140.1495919737166</v>
       </c>
       <c r="G194" t="n">
-        <v>-0.481239452032689</v>
+        <v>-0.4808679864375942</v>
       </c>
     </row>
     <row r="195">
@@ -4896,16 +4896,16 @@
         <v>-2.490589288669698</v>
       </c>
       <c r="D195" t="n">
-        <v>139.690214247675</v>
+        <v>139.6922871518602</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.948053637187285</v>
+        <v>-0.9468933674120938</v>
       </c>
       <c r="F195" t="n">
-        <v>139.4594122463039</v>
+        <v>139.460902389541</v>
       </c>
       <c r="G195" t="n">
-        <v>-0.4916704821446127</v>
+        <v>-0.4913960679277185</v>
       </c>
     </row>
     <row r="196">
@@ -4919,16 +4919,16 @@
         <v>-11.55616588535225</v>
       </c>
       <c r="D196" t="n">
-        <v>125.8185824514883</v>
+        <v>125.8160687657118</v>
       </c>
       <c r="E196" t="n">
-        <v>-9.930281710064449</v>
+        <v>-9.933417706207004</v>
       </c>
       <c r="F196" t="n">
-        <v>138.7913407181482</v>
+        <v>138.7930430857137</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.4790436998083791</v>
+        <v>-0.4788864064294129</v>
       </c>
     </row>
     <row r="197">
@@ -4942,16 +4942,16 @@
         <v>-24.42776813267562</v>
       </c>
       <c r="D197" t="n">
-        <v>106.1363364330326</v>
+        <v>106.1428355059561</v>
       </c>
       <c r="E197" t="n">
-        <v>-15.64335381543862</v>
+        <v>-15.63650291473514</v>
       </c>
       <c r="F197" t="n">
-        <v>138.1776556374565</v>
+        <v>138.1793723003113</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.4421638104483483</v>
+        <v>-0.4421480873672778</v>
       </c>
     </row>
     <row r="198">
@@ -4965,16 +4965,16 @@
         <v>-20.16997524911269</v>
       </c>
       <c r="D198" t="n">
-        <v>117.3343590892367</v>
+        <v>117.3329512386942</v>
       </c>
       <c r="E198" t="n">
-        <v>10.55060220895185</v>
+        <v>10.54250687707523</v>
       </c>
       <c r="F198" t="n">
-        <v>137.650254810076</v>
+        <v>137.651766323117</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.3816831490933703</v>
+        <v>-0.3818268735854669</v>
       </c>
     </row>
     <row r="199">
@@ -4988,16 +4988,16 @@
         <v>-12.15506526592874</v>
       </c>
       <c r="D199" t="n">
-        <v>124.1869338850719</v>
+        <v>124.1818426627035</v>
       </c>
       <c r="E199" t="n">
-        <v>5.840211553568575</v>
+        <v>5.837142381321714</v>
       </c>
       <c r="F199" t="n">
-        <v>137.234791770044</v>
+        <v>137.2358982108276</v>
       </c>
       <c r="G199" t="n">
-        <v>-0.3018251151116758</v>
+        <v>-0.3021160740598772</v>
       </c>
     </row>
     <row r="200">
@@ -5011,16 +5011,16 @@
         <v>-13.15828520146297</v>
       </c>
       <c r="D200" t="n">
-        <v>126.3901936727548</v>
+        <v>126.3818763348208</v>
       </c>
       <c r="E200" t="n">
-        <v>1.774147825987749</v>
+        <v>1.771622666361106</v>
       </c>
       <c r="F200" t="n">
-        <v>136.9497356125091</v>
+        <v>136.9502961581229</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.2077142056021275</v>
+        <v>-0.2081103096406411</v>
       </c>
     </row>
     <row r="201">
@@ -5034,16 +5034,16 @@
         <v>-11.39113115481285</v>
       </c>
       <c r="D201" t="n">
-        <v>128.7588114050895</v>
+        <v>128.7645164454792</v>
       </c>
       <c r="E201" t="n">
-        <v>1.874051825941048</v>
+        <v>1.885270404077599</v>
       </c>
       <c r="F201" t="n">
-        <v>136.8070028662324</v>
+        <v>136.8068885316611</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.1042227249569705</v>
+        <v>-0.1047150904268102</v>
       </c>
     </row>
     <row r="202">
@@ -5057,16 +5057,16 @@
         <v>-5.710378040976572</v>
       </c>
       <c r="D202" t="n">
-        <v>130.5994666834758</v>
+        <v>130.6020789810387</v>
       </c>
       <c r="E202" t="n">
-        <v>1.429537332862907</v>
+        <v>1.427072136241514</v>
       </c>
       <c r="F202" t="n">
-        <v>136.8087851599858</v>
+        <v>136.8079347111181</v>
       </c>
       <c r="G202" t="n">
-        <v>0.0013027796209375</v>
+        <v>0.0007647125580989567</v>
       </c>
     </row>
     <row r="203">
@@ -5080,16 +5080,16 @@
         <v>-7.267638332929982</v>
       </c>
       <c r="D203" t="n">
-        <v>133.4478940025828</v>
+        <v>133.444166574407</v>
       </c>
       <c r="E203" t="n">
-        <v>2.181040544377266</v>
+        <v>2.176142688954363</v>
       </c>
       <c r="F203" t="n">
-        <v>136.9494996091119</v>
+        <v>136.9478995563424</v>
       </c>
       <c r="G203" t="n">
-        <v>0.1028548341844848</v>
+        <v>0.1023075492805781</v>
       </c>
     </row>
     <row r="204">
@@ -5103,16 +5103,16 @@
         <v>-4.13957949896071</v>
       </c>
       <c r="D204" t="n">
-        <v>134.6844206580378</v>
+        <v>134.6844389954572</v>
       </c>
       <c r="E204" t="n">
-        <v>0.9265988532056069</v>
+        <v>0.929431726308283</v>
       </c>
       <c r="F204" t="n">
-        <v>137.2161263775568</v>
+        <v>137.2138275727328</v>
       </c>
       <c r="G204" t="n">
-        <v>0.1946898449471712</v>
+        <v>0.1941818876024515</v>
       </c>
     </row>
     <row r="205">
@@ -5126,16 +5126,16 @@
         <v>-1.40742220614487</v>
       </c>
       <c r="D205" t="n">
-        <v>136.9390965097797</v>
+        <v>136.942805600558</v>
       </c>
       <c r="E205" t="n">
-        <v>1.674043546184545</v>
+        <v>1.676783615052213</v>
       </c>
       <c r="F205" t="n">
-        <v>137.5917736470571</v>
+        <v>137.5888902814426</v>
       </c>
       <c r="G205" t="n">
-        <v>0.2737632080260788</v>
+        <v>0.2733417727240228</v>
       </c>
     </row>
     <row r="206">
@@ -5149,16 +5149,16 @@
         <v>-1.769758362157314</v>
       </c>
       <c r="D206" t="n">
-        <v>139.821095349318</v>
+        <v>139.8195900751862</v>
       </c>
       <c r="E206" t="n">
-        <v>2.104584383125729</v>
+        <v>2.10071968513581</v>
       </c>
       <c r="F206" t="n">
-        <v>138.0592086050403</v>
+        <v>138.0559054314555</v>
       </c>
       <c r="G206" t="n">
-        <v>0.3397259484293702</v>
+        <v>0.3394279502201059</v>
       </c>
     </row>
     <row r="207">
@@ -5172,16 +5172,16 @@
         <v>-2.120101289540577</v>
       </c>
       <c r="D207" t="n">
-        <v>138.3977793773793</v>
+        <v>138.3911872652127</v>
       </c>
       <c r="E207" t="n">
-        <v>-1.017955100682655</v>
+        <v>-1.021604203821103</v>
       </c>
       <c r="F207" t="n">
-        <v>138.6060847384259</v>
+        <v>138.6025420772449</v>
       </c>
       <c r="G207" t="n">
-        <v>0.3961170999828845</v>
+        <v>0.3959531061572541</v>
       </c>
     </row>
     <row r="208">
@@ -5195,16 +5195,16 @@
         <v>13.84111422285312</v>
       </c>
       <c r="D208" t="n">
-        <v>140.8414997897452</v>
+        <v>140.8495971760675</v>
       </c>
       <c r="E208" t="n">
-        <v>1.765722270515968</v>
+        <v>1.776420854128191</v>
       </c>
       <c r="F208" t="n">
-        <v>139.2221859740469</v>
+        <v>139.2186114894396</v>
       </c>
       <c r="G208" t="n">
-        <v>0.4444979719206765</v>
+        <v>0.4444863730215021</v>
       </c>
     </row>
     <row r="209">
@@ -5218,16 +5218,16 @@
         <v>29.99761617020937</v>
       </c>
       <c r="D209" t="n">
-        <v>139.5424321696422</v>
+        <v>139.5434514114115</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.9223613935113728</v>
+        <v>-0.9273336884473071</v>
       </c>
       <c r="F209" t="n">
-        <v>139.9034686415106</v>
+        <v>139.9001685203087</v>
       </c>
       <c r="G209" t="n">
-        <v>0.4893492101831098</v>
+        <v>0.4895588481865776</v>
       </c>
     </row>
     <row r="210">
@@ -5241,16 +5241,16 @@
         <v>15.37038797026475</v>
       </c>
       <c r="D210" t="n">
-        <v>138.9076826842862</v>
+        <v>138.9120661888236</v>
       </c>
       <c r="E210" t="n">
-        <v>-0.4548791901408111</v>
+        <v>-0.4524649606999276</v>
       </c>
       <c r="F210" t="n">
-        <v>140.6503615569519</v>
+        <v>140.6476576387823</v>
       </c>
       <c r="G210" t="n">
-        <v>0.5338630433496805</v>
+        <v>0.5343017999046795</v>
       </c>
     </row>
     <row r="211">
@@ -5264,16 +5264,16 @@
         <v>12.41881057893315</v>
       </c>
       <c r="D211" t="n">
-        <v>141.410798922503</v>
+        <v>141.4053961762199</v>
       </c>
       <c r="E211" t="n">
-        <v>1.801999853316949</v>
+        <v>1.794898064511652</v>
       </c>
       <c r="F211" t="n">
-        <v>141.4615663420817</v>
+        <v>141.4597375995639</v>
       </c>
       <c r="G211" t="n">
-        <v>0.576752719402962</v>
+        <v>0.5773860542115594</v>
       </c>
     </row>
     <row r="212">
@@ -5287,16 +5287,16 @@
         <v>11.73842029271386</v>
       </c>
       <c r="D212" t="n">
-        <v>141.5408083976177</v>
+        <v>141.5368421332924</v>
       </c>
       <c r="E212" t="n">
-        <v>0.09193744473927623</v>
+        <v>0.09295681821697155</v>
       </c>
       <c r="F212" t="n">
-        <v>142.3391034403107</v>
+        <v>142.3383715778855</v>
       </c>
       <c r="G212" t="n">
-        <v>0.6203360537567759</v>
+        <v>0.6211194741565285</v>
       </c>
     </row>
     <row r="213">
@@ -5310,16 +5310,16 @@
         <v>12.61428007521832</v>
       </c>
       <c r="D213" t="n">
-        <v>143.1490948006577</v>
+        <v>143.1476349054834</v>
       </c>
       <c r="E213" t="n">
-        <v>1.136270465915357</v>
+        <v>1.138073131993411</v>
       </c>
       <c r="F213" t="n">
-        <v>143.284282978078</v>
+        <v>143.2848146639426</v>
       </c>
       <c r="G213" t="n">
-        <v>0.6640336456549933</v>
+        <v>0.6649247673451208</v>
       </c>
     </row>
     <row r="214">
@@ -5333,16 +5333,16 @@
         <v>11.1036009811905</v>
       </c>
       <c r="D214" t="n">
-        <v>144.1365748215297</v>
+        <v>144.1420009810558</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6898262418264745</v>
+        <v>0.6946437335335398</v>
       </c>
       <c r="F214" t="n">
-        <v>144.2914495189675</v>
+        <v>144.2933041771794</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7029148766047877</v>
+        <v>0.7038355848120403</v>
       </c>
     </row>
     <row r="215">
@@ -5356,16 +5356,16 @@
         <v>6.219670020912438</v>
       </c>
       <c r="D215" t="n">
-        <v>143.337829259923</v>
+        <v>143.3300040300466</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.5541588334506353</v>
+        <v>-0.563331260481037</v>
       </c>
       <c r="F215" t="n">
-        <v>145.3479159820817</v>
+        <v>145.351078684308</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7321753760435756</v>
+        <v>0.733072482580166</v>
       </c>
     </row>
     <row r="216">
@@ -5379,16 +5379,16 @@
         <v>8.846324923586856</v>
       </c>
       <c r="D216" t="n">
-        <v>145.3893271779032</v>
+        <v>145.3824846694842</v>
       </c>
       <c r="E216" t="n">
-        <v>1.431232723819265</v>
+        <v>1.431996498798194</v>
       </c>
       <c r="F216" t="n">
-        <v>146.428018836351</v>
+        <v>146.4323885787371</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7431154736353474</v>
+        <v>0.7439297349678187</v>
       </c>
     </row>
     <row r="217">
@@ -5402,16 +5402,16 @@
         <v>9.992586094679389</v>
       </c>
       <c r="D217" t="n">
-        <v>149.8660232512943</v>
+        <v>149.8806909896185</v>
       </c>
       <c r="E217" t="n">
-        <v>3.079109148027959</v>
+        <v>3.09404969268523</v>
       </c>
       <c r="F217" t="n">
-        <v>147.4929473780423</v>
+        <v>147.498325169633</v>
       </c>
       <c r="G217" t="n">
-        <v>0.7272710169502705</v>
+        <v>0.7279377200917647</v>
       </c>
     </row>
     <row r="218">
@@ -5425,16 +5425,16 @@
         <v>6.171174984400896</v>
       </c>
       <c r="D218" t="n">
-        <v>148.2924918562783</v>
+        <v>148.2962395524488</v>
       </c>
       <c r="E218" t="n">
-        <v>-1.049958730390488</v>
+        <v>-1.057141801727779</v>
       </c>
       <c r="F218" t="n">
-        <v>148.4965995951519</v>
+        <v>148.5027111971158</v>
       </c>
       <c r="G218" t="n">
-        <v>0.6804747175721548</v>
+        <v>0.6809474116588277</v>
       </c>
     </row>
     <row r="219">
@@ -5448,16 +5448,16 @@
         <v>9.197016772619016</v>
       </c>
       <c r="D219" t="n">
-        <v>150.8432274055376</v>
+        <v>150.8430720686354</v>
       </c>
       <c r="E219" t="n">
-        <v>1.720070596515022</v>
+        <v>1.717395211013284</v>
       </c>
       <c r="F219" t="n">
-        <v>149.3935263572624</v>
+        <v>149.3999740877243</v>
       </c>
       <c r="G219" t="n">
-        <v>0.6040049163117622</v>
+        <v>0.6042064036241968</v>
       </c>
     </row>
     <row r="220">
@@ -5471,16 +5471,16 @@
         <v>5.463222831495251</v>
       </c>
       <c r="D220" t="n">
-        <v>150.4630682503714</v>
+        <v>150.4594758911337</v>
       </c>
       <c r="E220" t="n">
-        <v>-0.2520226871997489</v>
+        <v>-0.2543014884549111</v>
       </c>
       <c r="F220" t="n">
-        <v>150.1440750482579</v>
+        <v>150.1504249221493</v>
       </c>
       <c r="G220" t="n">
-        <v>0.5023970645157583</v>
+        <v>0.5023098825869932</v>
       </c>
     </row>
     <row r="221">
@@ -5494,16 +5494,16 @@
         <v>7.048335595742694</v>
       </c>
       <c r="D221" t="n">
-        <v>152.3783576998536</v>
+        <v>152.3762169955517</v>
       </c>
       <c r="E221" t="n">
-        <v>1.272929943376688</v>
+        <v>1.273925150320765</v>
       </c>
       <c r="F221" t="n">
-        <v>150.7199237261799</v>
+        <v>150.7257460924298</v>
       </c>
       <c r="G221" t="n">
-        <v>0.3835307372181962</v>
+        <v>0.3831631982252226</v>
       </c>
     </row>
     <row r="222">
@@ -5517,16 +5517,16 @@
         <v>8.943640525845753</v>
       </c>
       <c r="D222" t="n">
-        <v>152.1117988308375</v>
+        <v>152.1164035348158</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.1749322364670847</v>
+        <v>-0.1705078823052042</v>
       </c>
       <c r="F222" t="n">
-        <v>151.104328953342</v>
+        <v>151.1092704356261</v>
       </c>
       <c r="G222" t="n">
-        <v>0.2550460600420967</v>
+        <v>0.2544517795660006</v>
       </c>
     </row>
     <row r="223">
@@ -5540,16 +5540,16 @@
         <v>8.373774490054032</v>
       </c>
       <c r="D223" t="n">
-        <v>154.2742604415249</v>
+        <v>154.2717964418798</v>
       </c>
       <c r="E223" t="n">
-        <v>1.421626479542382</v>
+        <v>1.416936541344649</v>
       </c>
       <c r="F223" t="n">
-        <v>151.2947359716572</v>
+        <v>151.2985508501617</v>
       </c>
       <c r="G223" t="n">
-        <v>0.1260103000582991</v>
+        <v>0.1252606236466836</v>
       </c>
     </row>
     <row r="224">
@@ -5563,16 +5563,16 @@
         <v>7.034867574462633</v>
       </c>
       <c r="D224" t="n">
-        <v>152.6146249788266</v>
+        <v>152.6116456017</v>
       </c>
       <c r="E224" t="n">
-        <v>-1.075769514595981</v>
+        <v>-1.076120767677258</v>
       </c>
       <c r="F224" t="n">
-        <v>151.3049580849492</v>
+        <v>151.3074847915044</v>
       </c>
       <c r="G224" t="n">
-        <v>0.006756423629927788</v>
+        <v>0.00590484263891522</v>
       </c>
     </row>
     <row r="225">
@@ -5586,16 +5586,16 @@
         <v>7.441604964777015</v>
       </c>
       <c r="D225" t="n">
-        <v>151.5882186648882</v>
+        <v>151.5945331981538</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.672547807315782</v>
+        <v>-0.6664710281683139</v>
       </c>
       <c r="F225" t="n">
-        <v>151.1622768743108</v>
+        <v>151.1633918882115</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.09430041979080483</v>
+        <v>-0.09523184097036674</v>
       </c>
     </row>
     <row r="226">
@@ -5609,16 +5609,16 @@
         <v>5.575710315623583</v>
       </c>
       <c r="D226" t="n">
-        <v>150.7616216694861</v>
+        <v>150.7582865133789</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.5452910540689637</v>
+        <v>-0.5516338004627919</v>
       </c>
       <c r="F226" t="n">
-        <v>150.9029811432812</v>
+        <v>150.9025940219569</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.1715346820590491</v>
+        <v>-0.1725271330557665</v>
       </c>
     </row>
     <row r="227">
@@ -5632,16 +5632,16 @@
         <v>5.045801266890004</v>
       </c>
       <c r="D227" t="n">
-        <v>148.9897516363764</v>
+        <v>148.9821384040926</v>
       </c>
       <c r="E227" t="n">
-        <v>-1.175279234521731</v>
+        <v>-1.178142940175086</v>
       </c>
       <c r="F227" t="n">
-        <v>150.5667253111763</v>
+        <v>150.5647591112991</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.2228291512582081</v>
+        <v>-0.2238761453024485</v>
       </c>
     </row>
     <row r="228">
@@ -5655,16 +5655,16 @@
         <v>2.976390556758779</v>
       </c>
       <c r="D228" t="n">
-        <v>148.1411052418105</v>
+        <v>148.1289046369634</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.5696005163074447</v>
+        <v>-0.572708766479757</v>
       </c>
       <c r="F228" t="n">
-        <v>150.1915833929283</v>
+        <v>150.1880004026507</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.2491532690723663</v>
+        <v>-0.2502303400027217</v>
       </c>
     </row>
     <row r="229">
@@ -5678,16 +5678,16 @@
         <v>-0.7125401393221709</v>
       </c>
       <c r="D229" t="n">
-        <v>148.6168628955691</v>
+        <v>148.6366767327299</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3211516837153594</v>
+        <v>0.3427906909937217</v>
       </c>
       <c r="F229" t="n">
-        <v>149.8102857132862</v>
+        <v>149.8050838897285</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.2538741992249349</v>
+        <v>-0.2549581270777646</v>
       </c>
     </row>
     <row r="230">
@@ -5701,16 +5701,16 @@
         <v>2.432477417770906</v>
       </c>
       <c r="D230" t="n">
-        <v>149.5363819764523</v>
+        <v>149.5405719464588</v>
       </c>
       <c r="E230" t="n">
-        <v>0.618717864828966</v>
+        <v>0.6081239392577764</v>
       </c>
       <c r="F230" t="n">
-        <v>149.4449856892998</v>
+        <v>149.4382276244855</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.2438417510835178</v>
+        <v>-0.2448890623185207</v>
       </c>
     </row>
     <row r="231">
@@ -5724,16 +5724,16 @@
         <v>-0.4229617829554555</v>
       </c>
       <c r="D231" t="n">
-        <v>150.2042105117583</v>
+        <v>150.206171763387</v>
       </c>
       <c r="E231" t="n">
-        <v>0.4465993669762192</v>
+        <v>0.4450964766715915</v>
       </c>
       <c r="F231" t="n">
-        <v>149.1040513469149</v>
+        <v>149.0959060957389</v>
       </c>
       <c r="G231" t="n">
-        <v>-0.2281336779634047</v>
+        <v>-0.2290722622907415</v>
       </c>
     </row>
     <row r="232">
@@ -5747,16 +5747,16 @@
         <v>0.7368002375814031</v>
       </c>
       <c r="D232" t="n">
-        <v>151.0352344282044</v>
+        <v>151.0290832066008</v>
       </c>
       <c r="E232" t="n">
-        <v>0.5532627305284699</v>
+        <v>0.5478546144628726</v>
       </c>
       <c r="F232" t="n">
-        <v>148.7808253894636</v>
+        <v>148.7714875717152</v>
       </c>
       <c r="G232" t="n">
-        <v>-0.2167787893967099</v>
+        <v>-0.2175904976327026</v>
       </c>
     </row>
     <row r="233">
@@ -5770,16 +5770,16 @@
         <v>-4.821821470121468</v>
       </c>
       <c r="D233" t="n">
-        <v>147.5419265509701</v>
+        <v>147.5515547061282</v>
       </c>
       <c r="E233" t="n">
-        <v>-2.312909229729965</v>
+        <v>-2.30255552549139</v>
       </c>
       <c r="F233" t="n">
-        <v>148.4596362018175</v>
+        <v>148.4494696728585</v>
       </c>
       <c r="G233" t="n">
-        <v>-0.2158807674344843</v>
+        <v>-0.2164513537591728</v>
       </c>
     </row>
     <row r="234">
@@ -5793,16 +5793,16 @@
         <v>-6.605471486607451</v>
       </c>
       <c r="D234" t="n">
-        <v>145.608721383509</v>
+        <v>145.6114983965101</v>
       </c>
       <c r="E234" t="n">
-        <v>-1.310275128333327</v>
+        <v>-1.314832848411573</v>
       </c>
       <c r="F234" t="n">
-        <v>148.1182997271678</v>
+        <v>148.107820337392</v>
       </c>
       <c r="G234" t="n">
-        <v>-0.2299187061092001</v>
+        <v>-0.2301452044385255</v>
       </c>
     </row>
     <row r="235">
@@ -5816,16 +5816,16 @@
         <v>-5.487205304744203</v>
       </c>
       <c r="D235" t="n">
-        <v>145.9761982634973</v>
+        <v>145.9637930953682</v>
       </c>
       <c r="E235" t="n">
-        <v>0.2523728499891575</v>
+        <v>0.2419415380911616</v>
       </c>
       <c r="F235" t="n">
-        <v>147.7366269547274</v>
+        <v>147.726540514793</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.2576810381589967</v>
+        <v>-0.2574339570526996</v>
       </c>
     </row>
     <row r="236">
@@ -5839,16 +5839,16 @@
         <v>-1.470862442169829</v>
       </c>
       <c r="D236" t="n">
-        <v>148.7085273235832</v>
+        <v>148.7066246417496</v>
       </c>
       <c r="E236" t="n">
-        <v>1.871763405671012</v>
+        <v>1.87911775120102</v>
       </c>
       <c r="F236" t="n">
-        <v>147.3032055765617</v>
+        <v>147.2943044737198</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.2933743561767344</v>
+        <v>-0.292592001116998</v>
       </c>
     </row>
     <row r="237">
@@ -5862,16 +5862,16 @@
         <v>0.3013489700748551</v>
       </c>
       <c r="D237" t="n">
-        <v>150.0715602947967</v>
+        <v>150.0768790046068</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9165802363489295</v>
+        <v>0.9214480969884642</v>
       </c>
       <c r="F237" t="n">
-        <v>146.8145878162389</v>
+        <v>146.8076626079236</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.3317088439523941</v>
+        <v>-0.3303874291235798</v>
       </c>
     </row>
     <row r="238">
@@ -5879,22 +5879,22 @@
         <v>45170</v>
       </c>
       <c r="B238" t="n">
-        <v>148.4123796322611</v>
+        <v>148.4123796322612</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.5107916169959204</v>
+        <v>-0.5107916169958981</v>
       </c>
       <c r="D238" t="n">
-        <v>149.7061618401914</v>
+        <v>149.702745812246</v>
       </c>
       <c r="E238" t="n">
-        <v>-0.2434828117249488</v>
+        <v>-0.249294358226404</v>
       </c>
       <c r="F238" t="n">
-        <v>146.2805573138676</v>
+        <v>146.2762721411204</v>
       </c>
       <c r="G238" t="n">
-        <v>-0.3637448500960483</v>
+        <v>-0.3619637131765163</v>
       </c>
     </row>
     <row r="239">
@@ -5908,16 +5908,16 @@
         <v>0.6546489858882509</v>
       </c>
       <c r="D239" t="n">
-        <v>147.8310782482043</v>
+        <v>147.8175886299227</v>
       </c>
       <c r="E239" t="n">
-        <v>-1.252509294833648</v>
+        <v>-1.259266937353032</v>
       </c>
       <c r="F239" t="n">
-        <v>145.7244458132743</v>
+        <v>145.7232399536497</v>
       </c>
       <c r="G239" t="n">
-        <v>-0.380167748062421</v>
+        <v>-0.3780737500181597</v>
       </c>
     </row>
     <row r="240">
@@ -5931,16 +5931,16 @@
         <v>-1.124189048551316</v>
       </c>
       <c r="D240" t="n">
-        <v>146.3815407092691</v>
+        <v>146.3721040008119</v>
       </c>
       <c r="E240" t="n">
-        <v>-0.9805364041933551</v>
+        <v>-0.9778840546031065</v>
       </c>
       <c r="F240" t="n">
-        <v>145.17812854123</v>
+        <v>145.1800686464252</v>
       </c>
       <c r="G240" t="n">
-        <v>-0.3748974779045344</v>
+        <v>-0.3727417173796321</v>
       </c>
     </row>
     <row r="241">
@@ -5954,16 +5954,16 @@
         <v>-4.677891193168204</v>
       </c>
       <c r="D241" t="n">
-        <v>142.9908931629124</v>
+        <v>143.0138194896783</v>
       </c>
       <c r="E241" t="n">
-        <v>-2.316308142357215</v>
+        <v>-2.294347364928873</v>
       </c>
       <c r="F241" t="n">
-        <v>144.6862233225339</v>
+        <v>144.6909480329792</v>
       </c>
       <c r="G241" t="n">
-        <v>-0.3388287365588938</v>
+        <v>-0.3369061731450129</v>
       </c>
     </row>
     <row r="242">
@@ -5977,16 +5977,16 @@
         <v>-3.957973283918947</v>
       </c>
       <c r="D242" t="n">
-        <v>143.0574156896178</v>
+        <v>143.0363234344028</v>
       </c>
       <c r="E242" t="n">
-        <v>0.0465222121730724</v>
+        <v>0.01573550360713938</v>
       </c>
       <c r="F242" t="n">
-        <v>144.2976417090826</v>
+        <v>144.3043761085799</v>
       </c>
       <c r="G242" t="n">
-        <v>-0.2685684956922785</v>
+        <v>-0.2671707730542816</v>
       </c>
     </row>
     <row r="243">
@@ -6000,16 +6000,16 @@
         <v>-2.76976388254716</v>
       </c>
       <c r="D243" t="n">
-        <v>143.8710263395235</v>
+        <v>143.9064389646668</v>
       </c>
       <c r="E243" t="n">
-        <v>0.5687301465524319</v>
+        <v>0.6083178799425992</v>
       </c>
       <c r="F243" t="n">
-        <v>144.0560240699473</v>
+        <v>144.0637717834372</v>
       </c>
       <c r="G243" t="n">
-        <v>-0.1674439278934514</v>
+        <v>-0.1667339076132146</v>
       </c>
     </row>
     <row r="244">
@@ -6023,16 +6023,16 @@
         <v>-8.170308484600453</v>
       </c>
       <c r="D244" t="n">
-        <v>142.3339723461691</v>
+        <v>142.3196519762666</v>
       </c>
       <c r="E244" t="n">
-        <v>-1.068355479530014</v>
+        <v>-1.102651833938983</v>
       </c>
       <c r="F244" t="n">
-        <v>143.9988809380349</v>
+        <v>144.0065063265247</v>
       </c>
       <c r="G244" t="n">
-        <v>-0.03966729769289135</v>
+        <v>-0.03975007470902181</v>
       </c>
     </row>
     <row r="245">
@@ -6046,16 +6046,16 @@
         <v>-1.867676993792655</v>
       </c>
       <c r="D245" t="n">
-        <v>141.0948492677061</v>
+        <v>141.1042633996142</v>
       </c>
       <c r="E245" t="n">
-        <v>-0.8705743667783095</v>
+        <v>-0.8539850679617378</v>
       </c>
       <c r="F245" t="n">
-        <v>144.1490508720109</v>
+        <v>144.1553409917042</v>
       </c>
       <c r="G245" t="n">
-        <v>0.1042854868022136</v>
+        <v>0.1033527366062437</v>
       </c>
     </row>
     <row r="246">
@@ -6069,16 +6069,16 @@
         <v>1.923300218212187</v>
       </c>
       <c r="D246" t="n">
-        <v>143.1200921766983</v>
+        <v>143.1310786224424</v>
       </c>
       <c r="E246" t="n">
-        <v>1.435376925170173</v>
+        <v>1.436395452551409</v>
       </c>
       <c r="F246" t="n">
-        <v>144.5086089917715</v>
+        <v>144.512326930998</v>
       </c>
       <c r="G246" t="n">
-        <v>0.2494349547121688</v>
+        <v>0.2476397591916646</v>
       </c>
     </row>
     <row r="247">
@@ -6092,16 +6092,16 @@
         <v>-3.432836908604375</v>
       </c>
       <c r="D247" t="n">
-        <v>143.3343357316054</v>
+        <v>143.3139351539781</v>
       </c>
       <c r="E247" t="n">
-        <v>0.1496949531325065</v>
+        <v>0.1277545962033777</v>
       </c>
       <c r="F247" t="n">
-        <v>145.061366571102</v>
+        <v>145.0615404687491</v>
       </c>
       <c r="G247" t="n">
-        <v>0.3825084077599294</v>
+        <v>0.3800461520582887</v>
       </c>
     </row>
     <row r="248">
@@ -6115,16 +6115,16 @@
         <v>-0.3671180299617438</v>
       </c>
       <c r="D248" t="n">
-        <v>147.2450322782883</v>
+        <v>147.2266788951813</v>
       </c>
       <c r="E248" t="n">
-        <v>2.728373858728195</v>
+        <v>2.730190708251334</v>
       </c>
       <c r="F248" t="n">
-        <v>145.7750125046769</v>
+        <v>145.7710750713689</v>
       </c>
       <c r="G248" t="n">
-        <v>0.4919614025731267</v>
+        <v>0.4891266150400364</v>
       </c>
     </row>
     <row r="249">
@@ -6138,16 +6138,16 @@
         <v>-3.05480793285795</v>
       </c>
       <c r="D249" t="n">
-        <v>147.9974800216081</v>
+        <v>148.0281973036644</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5110174052580074</v>
+        <v>0.5444111179426114</v>
       </c>
       <c r="F249" t="n">
-        <v>146.6037699126494</v>
+        <v>146.5955822974162</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5685181525509675</v>
+        <v>0.5656178536404655</v>
       </c>
     </row>
     <row r="250">
@@ -6158,19 +6158,19 @@
         <v>144.7966986918363</v>
       </c>
       <c r="C250" t="n">
-        <v>-2.436239449420474</v>
+        <v>-2.436239449420496</v>
       </c>
       <c r="D250" t="n">
-        <v>147.8286949884446</v>
+        <v>147.8163310895239</v>
       </c>
       <c r="E250" t="n">
-        <v>-0.1140458831724089</v>
+        <v>-0.1431255787746277</v>
       </c>
       <c r="F250" t="n">
-        <v>147.495321779401</v>
+        <v>147.4831256286563</v>
       </c>
       <c r="G250" t="n">
-        <v>0.6081370672001096</v>
+        <v>0.6054366150266555</v>
       </c>
     </row>
     <row r="251">
@@ -6184,16 +6184,16 @@
         <v>0.4000494277979438</v>
       </c>
       <c r="D251" t="n">
-        <v>149.1071950340242</v>
+        <v>149.0937404221376</v>
       </c>
       <c r="E251" t="n">
-        <v>0.8648524196737117</v>
+        <v>0.8641868751566362</v>
       </c>
       <c r="F251" t="n">
-        <v>148.3929144635432</v>
+        <v>148.3778187125253</v>
       </c>
       <c r="G251" t="n">
-        <v>0.6085567144188619</v>
+        <v>0.6066409835398856</v>
       </c>
     </row>
     <row r="252">
@@ -6207,16 +6207,16 @@
         <v>1.238246952980671</v>
       </c>
       <c r="D252" t="n">
-        <v>150.8702196228531</v>
+        <v>150.8676442579033</v>
       </c>
       <c r="E252" t="n">
-        <v>1.182387334445223</v>
+        <v>1.189790953492142</v>
       </c>
       <c r="F252" t="n">
-        <v>149.2453432431954</v>
+        <v>149.2291019213164</v>
       </c>
       <c r="G252" t="n">
-        <v>0.5744403516392715</v>
+        <v>0.5737267309747995</v>
       </c>
     </row>
     <row r="253">
@@ -6230,16 +6230,16 @@
         <v>6.699305839770497</v>
       </c>
       <c r="D253" t="n">
-        <v>151.4463248853266</v>
+        <v>151.4623548621935</v>
       </c>
       <c r="E253" t="n">
-        <v>0.3818548577139147</v>
+        <v>0.3941936040795735</v>
       </c>
       <c r="F253" t="n">
-        <v>150.0136848983043</v>
+        <v>149.9959504285912</v>
       </c>
       <c r="G253" t="n">
-        <v>0.5148178418250327</v>
+        <v>0.5138732977694627</v>
       </c>
     </row>
     <row r="254">
@@ -6253,16 +6253,16 @@
         <v>6.641267235606474</v>
       </c>
       <c r="D254" t="n">
-        <v>151.5509588186135</v>
+        <v>151.4789777824147</v>
       </c>
       <c r="E254" t="n">
-        <v>0.06908978039987801</v>
+        <v>0.01097495165471862</v>
       </c>
       <c r="F254" t="n">
-        <v>150.671353303254</v>
+        <v>150.6520380804276</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4384056063921449</v>
+        <v>0.437403576537676</v>
       </c>
     </row>
     <row r="255">
@@ -6276,16 +6276,16 @@
         <v>5.949232135689031</v>
       </c>
       <c r="D255" t="n">
-        <v>153.4167608129367</v>
+        <v>153.5157373443335</v>
       </c>
       <c r="E255" t="n">
-        <v>1.231138363536388</v>
+        <v>1.344582325373533</v>
       </c>
       <c r="F255" t="n">
-        <v>151.2070214919885</v>
+        <v>151.1877556493311</v>
       </c>
       <c r="G255" t="n">
-        <v>0.3555209248412572</v>
+        <v>0.3555992841049793</v>
       </c>
     </row>
     <row r="256">
@@ -6299,16 +6299,16 @@
         <v>5.768685957403763</v>
       </c>
       <c r="D256" t="n">
-        <v>149.4556873103234</v>
+        <v>149.4286918151571</v>
       </c>
       <c r="E256" t="n">
-        <v>-2.581904012067548</v>
+        <v>-2.662297429487115</v>
       </c>
       <c r="F256" t="n">
-        <v>151.6243118363574</v>
+        <v>151.6091557136406</v>
       </c>
       <c r="G256" t="n">
-        <v>0.2759728617437229</v>
+        <v>0.2787263178156474</v>
       </c>
     </row>
     <row r="257">
@@ -6322,16 +6322,16 @@
         <v>7.933203690735868</v>
       </c>
       <c r="D257" t="n">
-        <v>152.508372543981</v>
+        <v>152.5220646516665</v>
       </c>
       <c r="E257" t="n">
-        <v>2.042535341809448</v>
+        <v>2.070133117631712</v>
       </c>
       <c r="F257" t="n">
-        <v>151.938806946036</v>
+        <v>151.9342892896101</v>
       </c>
       <c r="G257" t="n">
-        <v>0.2074173368832977</v>
+        <v>0.2144551062494005</v>
       </c>
     </row>
     <row r="258">
@@ -6345,16 +6345,16 @@
         <v>5.297891335236438</v>
       </c>
       <c r="D258" t="n">
-        <v>152.4631812003061</v>
+        <v>152.4585690449656</v>
       </c>
       <c r="E258" t="n">
-        <v>-0.02963204112734763</v>
+        <v>-0.04163044005855987</v>
       </c>
       <c r="F258" t="n">
-        <v>152.1773372215229</v>
+        <v>152.18901419738</v>
       </c>
       <c r="G258" t="n">
-        <v>0.1569910151864917</v>
+        <v>0.1676546544962632</v>
       </c>
     </row>
     <row r="259">
@@ -6368,16 +6368,16 @@
         <v>6.400830482237607</v>
       </c>
       <c r="D259" t="n">
-        <v>150.9735911041198</v>
+        <v>150.9645111518067</v>
       </c>
       <c r="E259" t="n">
-        <v>-0.9770162766243762</v>
+        <v>-0.9799763322705046</v>
       </c>
       <c r="F259" t="n">
-        <v>152.3675709004486</v>
+        <v>152.4018237753019</v>
       </c>
       <c r="G259" t="n">
-        <v>0.1250078903987983</v>
+        <v>0.1398324176316024</v>
       </c>
     </row>
     <row r="260">
@@ -6391,16 +6391,16 @@
         <v>2.752703174786197</v>
       </c>
       <c r="D260" t="n">
-        <v>151.542066633669</v>
+        <v>151.5245982214525</v>
       </c>
       <c r="E260" t="n">
-        <v>0.3765397149207983</v>
+        <v>0.3710057849839021</v>
       </c>
       <c r="F260" t="n">
-        <v>152.5352284212528</v>
+        <v>152.6003899846033</v>
       </c>
       <c r="G260" t="n">
-        <v>0.1100349108497323</v>
+        <v>0.1302912290565228</v>
       </c>
     </row>
     <row r="261">
@@ -6414,16 +6414,16 @@
         <v>2.101384741980494</v>
       </c>
       <c r="D261" t="n">
-        <v>152.4776457529625</v>
+        <v>152.534612021521</v>
       </c>
       <c r="E261" t="n">
-        <v>0.6173725488086257</v>
+        <v>0.6665675487172784</v>
       </c>
       <c r="F261" t="n">
-        <v>152.7007340708299</v>
+        <v>152.8024086254374</v>
       </c>
       <c r="G261" t="n">
-        <v>0.1085032299030786</v>
+        <v>0.1323840921077846</v>
       </c>
     </row>
     <row r="262">
@@ -6437,16 +6437,16 @@
         <v>4.770482265769438</v>
       </c>
       <c r="D262" t="n">
-        <v>153.2289688740294</v>
+        <v>153.1894710177184</v>
       </c>
       <c r="E262" t="n">
-        <v>0.4927431279232453</v>
+        <v>0.4293182953814201</v>
       </c>
       <c r="F262" t="n">
-        <v>152.8791436474515</v>
+        <v>153.0159325013311</v>
       </c>
       <c r="G262" t="n">
-        <v>0.1168360962422677</v>
+        <v>0.1397385537404316</v>
       </c>
     </row>
     <row r="263">
@@ -6460,16 +6460,16 @@
         <v>3.193778668065428</v>
       </c>
       <c r="D263" t="n">
-        <v>153.2613988120184</v>
+        <v>153.2419815455886</v>
       </c>
       <c r="E263" t="n">
-        <v>0.02116436482431094</v>
+        <v>0.03427815731806838</v>
       </c>
       <c r="F263" t="n">
-        <v>153.0806149505581</v>
+        <v>153.2408227663313</v>
       </c>
       <c r="G263" t="n">
-        <v>0.1317846884145268</v>
+        <v>0.1469717965469242</v>
       </c>
     </row>
     <row r="264">
@@ -6483,16 +6483,16 @@
         <v>-0.1409470274271185</v>
       </c>
       <c r="D264" t="n">
-        <v>152.954022757144</v>
+        <v>152.9624752924261</v>
       </c>
       <c r="E264" t="n">
-        <v>-0.2005567333046687</v>
+        <v>-0.1823953529857758</v>
       </c>
       <c r="F264" t="n">
-        <v>153.3108821940772</v>
+        <v>153.4676717963636</v>
       </c>
       <c r="G264" t="n">
-        <v>0.1504222096269325</v>
+        <v>0.1480343331086376</v>
       </c>
     </row>
     <row r="265">
@@ -6506,16 +6506,16 @@
         <v>3.480453901317304</v>
       </c>
       <c r="D265" t="n">
-        <v>155.9893449969597</v>
+        <v>156.0003097281395</v>
       </c>
       <c r="E265" t="n">
-        <v>1.984467086972375</v>
+        <v>1.985999788448667</v>
       </c>
       <c r="F265" t="n">
-        <v>153.5730458549637</v>
+        <v>153.6851890499165</v>
       </c>
       <c r="G265" t="n">
-        <v>0.1710013386750919</v>
+        <v>0.1417349015637948</v>
       </c>
     </row>
     <row r="266">
@@ -6523,22 +6523,22 @@
         <v>46023</v>
       </c>
       <c r="B266" t="n">
-        <v>149.4860204320602</v>
+        <v>149.4257679886021</v>
       </c>
       <c r="C266" t="n">
-        <v>2.040549789840673</v>
+        <v>1.999420910773031</v>
       </c>
       <c r="D266" t="n">
-        <v>155.985708376939</v>
+        <v>155.8163239058146</v>
       </c>
       <c r="E266" t="n">
-        <v>-0.002331325912563464</v>
+        <v>-0.1179393955342278</v>
       </c>
       <c r="F266" t="n">
-        <v>153.8628699113328</v>
+        <v>153.876592901774</v>
       </c>
       <c r="G266" t="n">
-        <v>0.188720653911334</v>
+        <v>0.1245428092588208</v>
       </c>
     </row>
     <row r="267">
@@ -6546,22 +6546,22 @@
         <v>46054</v>
       </c>
       <c r="B267" t="n">
-        <v>139.3430347649106</v>
+        <v>139.3086576611261</v>
       </c>
       <c r="C267" t="n">
-        <v>-1.457932828717912</v>
+        <v>-1.482243989128651</v>
       </c>
       <c r="D267" t="n">
-        <v>152.5828198259359</v>
+        <v>152.7108484976979</v>
       </c>
       <c r="E267" t="n">
-        <v>-2.181538671978844</v>
+        <v>-1.993035986392488</v>
       </c>
       <c r="F267" t="n">
-        <v>154.1735380312101</v>
+        <v>154.0297380085279</v>
       </c>
       <c r="G267" t="n">
-        <v>0.2019123392514421</v>
+        <v>0.09952462805804529</v>
       </c>
     </row>
     <row r="268">
@@ -6569,22 +6569,22 @@
         <v>46082</v>
       </c>
       <c r="B268" t="n">
-        <v>160.2374480336475</v>
+        <v>160.3320775808902</v>
       </c>
       <c r="C268" t="n">
-        <v>6.392242700194251</v>
+        <v>6.455073517087562</v>
       </c>
       <c r="D268" t="n">
-        <v>156.7369566403329</v>
+        <v>156.7783124397283</v>
       </c>
       <c r="E268" t="n">
-        <v>2.722545578287261</v>
+        <v>2.663506870693433</v>
       </c>
       <c r="F268" t="n">
-        <v>154.4973135742296</v>
+        <v>154.141796052647</v>
       </c>
       <c r="G268" t="n">
-        <v>0.2100072082109605</v>
+        <v>0.07275091522449539</v>
       </c>
     </row>
     <row r="269">
@@ -6592,22 +6592,22 @@
         <v>46113</v>
       </c>
       <c r="B269" t="n">
-        <v>162.3029965582245</v>
+        <v>162.3664218860946</v>
       </c>
       <c r="C269" t="n">
-        <v>2.116475681368302</v>
+        <v>2.15638111188019</v>
       </c>
       <c r="D269" t="n">
-        <v>154.6096598657605</v>
+        <v>154.651993750656</v>
       </c>
       <c r="E269" t="n">
-        <v>-1.357240066523691</v>
+        <v>-1.356258181366576</v>
       </c>
       <c r="F269" t="n">
-        <v>154.8201721631755</v>
+        <v>154.2117125803676</v>
       </c>
       <c r="G269" t="n">
-        <v>0.2089735940882909</v>
+        <v>0.04535857860175074</v>
       </c>
     </row>
     <row r="270">
@@ -6615,22 +6615,22 @@
         <v>46143</v>
       </c>
       <c r="B270" t="n">
-        <v>166.2683299873349</v>
+        <v>166.2509495566577</v>
       </c>
       <c r="C270" t="n">
-        <v>0.7231731165137756</v>
+        <v>0.712644279614616</v>
       </c>
       <c r="D270" t="n">
-        <v>153.7018967954664</v>
+        <v>153.6601711720324</v>
       </c>
       <c r="E270" t="n">
-        <v>-0.5871321824795439</v>
+        <v>-0.6413254395043366</v>
       </c>
       <c r="F270" t="n">
-        <v>155.1393244307295</v>
+        <v>154.2507050408616</v>
       </c>
       <c r="G270" t="n">
-        <v>0.2061438526354653</v>
+        <v>0.02528501878458211</v>
       </c>
     </row>
     <row r="271">
@@ -6638,22 +6638,22 @@
         <v>46174</v>
       </c>
       <c r="B271" t="n">
-        <v>161.7041890303425</v>
+        <v>161.6581441331496</v>
       </c>
       <c r="C271" t="n">
-        <v>3.134774046184408</v>
+        <v>3.105406655664456</v>
       </c>
       <c r="D271" t="n">
-        <v>154.1172638255603</v>
+        <v>154.1172638255897</v>
       </c>
       <c r="E271" t="n">
-        <v>0.2702419675709056</v>
+        <v>0.2974698323390257</v>
       </c>
       <c r="F271" t="n">
-        <v>155.4545235936482</v>
+        <v>154.2748184621527</v>
       </c>
       <c r="G271" t="n">
-        <v>0.2031716742839418</v>
+        <v>0.01563261658008575</v>
       </c>
     </row>
     <row r="272">
@@ -6661,22 +6661,45 @@
         <v>46204</v>
       </c>
       <c r="B272" t="n">
-        <v>151.5541509337364</v>
+        <v>151.5121383384529</v>
       </c>
       <c r="C272" t="n">
-        <v>-1.441765040806708</v>
+        <v>-1.469086544122067</v>
       </c>
       <c r="D272" t="n">
-        <v>149.6479229845689</v>
+        <v>149.7918948657556</v>
       </c>
       <c r="E272" t="n">
-        <v>-2.899961191920819</v>
+        <v>-2.806544090173479</v>
       </c>
       <c r="F272" t="n">
-        <v>155.7648547463437</v>
+        <v>154.2959675312639</v>
       </c>
       <c r="G272" t="n">
-        <v>0.1996282549530104</v>
+        <v>0.0137086981025103</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B273" t="n">
+        <v>147.7531958840131</v>
+      </c>
+      <c r="C273" t="n">
+        <v>-1.744290968177853</v>
+      </c>
+      <c r="D273" t="n">
+        <v>149.8907351965427</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.06598509944459874</v>
+      </c>
+      <c r="F273" t="n">
+        <v>154.319967395067</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0.01555443359086972</v>
       </c>
     </row>
   </sheetData>
@@ -6713,7 +6736,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Índice base 2004=100; variaciones en %</t>
+          <t>Índice base 2004=100</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6772,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16T21:08:21Z</t>
+          <t>2026-10-21T19:38:26Z</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6784,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
